--- a/metadata/C3H10_10X_Metadata.xlsx
+++ b/metadata/C3H10_10X_Metadata.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,14 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gardeux\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA539A46-C8E2-41C1-B384-6189AAC22AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE18494-B7A5-40EF-AB0A-D401249857CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C3H10_10X_Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -6762,7 +6773,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -7317,7 +7328,7 @@
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="42"/>
+    <cellStyle name="Normal 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
@@ -7633,8 +7644,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J645"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L645"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -7649,7 +7660,7 @@
     <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -7678,7 +7689,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -7707,7 +7718,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -7736,7 +7747,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -7765,7 +7776,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7794,7 +7805,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -7823,7 +7834,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -7852,7 +7863,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -7881,7 +7892,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -7910,7 +7921,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -7938,8 +7949,16 @@
       <c r="I10" s="11" t="s">
         <v>1861</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K10">
+        <f>SUM(G9:G12)</f>
+        <v>261</v>
+      </c>
+      <c r="L10">
+        <f>SUM(H9:H12)</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -7968,7 +7987,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -7997,7 +8016,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -8026,7 +8045,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -8055,7 +8074,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -8084,7 +8103,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>62</v>
       </c>

--- a/metadata/C3H10_10X_Metadata.xlsx
+++ b/metadata/C3H10_10X_Metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gardeux\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\TF-seq\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE18494-B7A5-40EF-AB0A-D401249857CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544F7C1D-62E6-47C3-9648-C6C8D7D22C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C3H10_10X_Metadata" sheetId="1" r:id="rId1"/>
@@ -5616,9 +5616,6 @@
     <t>comment</t>
   </si>
   <si>
-    <t>Matureadipo</t>
-  </si>
-  <si>
     <t>not found</t>
   </si>
   <si>
@@ -6058,22 +6055,6 @@
   </si>
   <si>
     <t>less than 8 cells: excluded</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">None called as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Matureadipo</t>
-    </r>
   </si>
   <si>
     <t>2 missing?</t>
@@ -6754,6 +6735,12 @@
     <t>D0_osteo</t>
   </si>
   <si>
+    <t>Adipo_ref</t>
+  </si>
+  <si>
+    <t>None called as Adipo_ref</t>
+  </si>
+  <si>
     <r>
       <t>Renamed</t>
     </r>
@@ -6766,7 +6753,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Myod1</t>
+      <t xml:space="preserve"> Myo_ref</t>
     </r>
   </si>
 </sst>
@@ -7680,7 +7667,7 @@
         <v>1850</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>1859</v>
@@ -7773,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -7802,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -7831,7 +7818,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -7918,7 +7905,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -7947,7 +7934,7 @@
         <v>14</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
       <c r="K10">
         <f>SUM(G9:G12)</f>
@@ -7984,7 +7971,7 @@
         <v>16</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -8013,7 +8000,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -8042,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -8071,7 +8058,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -8100,7 +8087,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -8831,7 +8818,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -9152,7 +9139,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -9181,7 +9168,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -9210,7 +9197,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -9297,7 +9284,7 @@
         <v>17</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -9326,7 +9313,7 @@
         <v>26</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -9355,7 +9342,7 @@
         <v>11</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -9384,7 +9371,7 @@
         <v>7</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -9413,7 +9400,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -9442,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -9471,7 +9458,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -9500,7 +9487,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -9555,7 +9542,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -9714,7 +9701,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -9821,7 +9808,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -9850,7 +9837,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -9879,7 +9866,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -10064,7 +10051,7 @@
         <v>39</v>
       </c>
       <c r="I88" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -10093,7 +10080,7 @@
         <v>63</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -10122,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -10177,7 +10164,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -10232,7 +10219,7 @@
         <v>53</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -10261,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -10342,7 +10329,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -10371,7 +10358,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -10400,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -10455,7 +10442,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -10484,7 +10471,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -10565,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -10620,7 +10607,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -10649,7 +10636,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -10678,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -10707,7 +10694,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -10840,7 +10827,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -10895,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -10950,7 +10937,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -11005,7 +10992,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -11060,7 +11047,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -11089,7 +11076,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -11326,7 +11313,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
@@ -11407,7 +11394,7 @@
         <v>0</v>
       </c>
       <c r="I137" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -11541,7 +11528,7 @@
         <v>93</v>
       </c>
       <c r="I142" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
@@ -11570,7 +11557,7 @@
         <v>56</v>
       </c>
       <c r="I143" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
@@ -11599,7 +11586,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -11732,7 +11719,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -12047,7 +12034,7 @@
         <v>105</v>
       </c>
       <c r="I161" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -12856,7 +12843,7 @@
         <v>78</v>
       </c>
       <c r="I192" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -12989,7 +12976,7 @@
         <v>40</v>
       </c>
       <c r="I197" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -13362,7 +13349,7 @@
         <v>0</v>
       </c>
       <c r="I211" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -13391,7 +13378,7 @@
         <v>0</v>
       </c>
       <c r="I212" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -13420,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="I213" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -13449,7 +13436,7 @@
         <v>0</v>
       </c>
       <c r="I214" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -13478,7 +13465,7 @@
         <v>0</v>
       </c>
       <c r="I215" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
@@ -13507,7 +13494,7 @@
         <v>37</v>
       </c>
       <c r="I216" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -13536,7 +13523,7 @@
         <v>0</v>
       </c>
       <c r="I217" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -13565,7 +13552,7 @@
         <v>0</v>
       </c>
       <c r="I218" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
@@ -13623,7 +13610,7 @@
         <v>37</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
@@ -13643,7 +13630,7 @@
         <v>462</v>
       </c>
       <c r="F221" s="12" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="G221" s="1">
         <v>0</v>
@@ -13652,7 +13639,7 @@
         <v>0</v>
       </c>
       <c r="I221" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -13681,7 +13668,7 @@
         <v>12</v>
       </c>
       <c r="I222" s="11" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -13765,7 +13752,7 @@
         <v>33</v>
       </c>
       <c r="I225" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
@@ -13846,7 +13833,7 @@
         <v>23</v>
       </c>
       <c r="I228" s="3" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
@@ -14057,7 +14044,7 @@
         <v>64</v>
       </c>
       <c r="I236" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
@@ -14138,7 +14125,7 @@
         <v>22</v>
       </c>
       <c r="I239" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
@@ -14167,7 +14154,7 @@
         <v>38</v>
       </c>
       <c r="I240" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
@@ -14508,7 +14495,7 @@
         <v>73</v>
       </c>
       <c r="I253" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
@@ -14537,7 +14524,7 @@
         <v>98</v>
       </c>
       <c r="I254" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
@@ -14800,7 +14787,7 @@
         <v>48</v>
       </c>
       <c r="I264" s="8" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
@@ -15193,7 +15180,7 @@
         <v>19</v>
       </c>
       <c r="I279" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
@@ -15378,7 +15365,7 @@
         <v>18</v>
       </c>
       <c r="I286" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
@@ -15615,7 +15602,7 @@
         <v>61</v>
       </c>
       <c r="I295" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
@@ -15910,7 +15897,7 @@
         <v>0</v>
       </c>
       <c r="I306" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
@@ -15939,7 +15926,7 @@
         <v>0</v>
       </c>
       <c r="I307" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
@@ -15968,7 +15955,7 @@
         <v>0</v>
       </c>
       <c r="I308" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
@@ -15997,7 +15984,7 @@
         <v>0</v>
       </c>
       <c r="I309" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
@@ -16026,7 +16013,7 @@
         <v>0</v>
       </c>
       <c r="I310" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
@@ -16055,7 +16042,7 @@
         <v>21</v>
       </c>
       <c r="I311" s="13" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
@@ -16084,7 +16071,7 @@
         <v>0</v>
       </c>
       <c r="I312" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
@@ -16113,7 +16100,7 @@
         <v>0</v>
       </c>
       <c r="I313" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
@@ -16171,7 +16158,7 @@
         <v>27</v>
       </c>
       <c r="I315" s="13" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
@@ -16191,7 +16178,7 @@
         <v>743</v>
       </c>
       <c r="F316" s="14" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="G316" s="1">
         <v>0</v>
@@ -16200,7 +16187,7 @@
         <v>0</v>
       </c>
       <c r="I316" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
@@ -16229,7 +16216,7 @@
         <v>5</v>
       </c>
       <c r="I317" s="13" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
@@ -16313,7 +16300,7 @@
         <v>31</v>
       </c>
       <c r="I320" s="13" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
@@ -16394,7 +16381,7 @@
         <v>63</v>
       </c>
       <c r="I323" s="3" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
@@ -16423,7 +16410,7 @@
         <v>60</v>
       </c>
       <c r="I324" s="5" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
@@ -16634,7 +16621,7 @@
         <v>0</v>
       </c>
       <c r="I332" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
@@ -16767,7 +16754,7 @@
         <v>72</v>
       </c>
       <c r="I337" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
@@ -16848,7 +16835,7 @@
         <v>68</v>
       </c>
       <c r="I340" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
@@ -16877,7 +16864,7 @@
         <v>90</v>
       </c>
       <c r="I341" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
@@ -16906,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="I342" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.25">
@@ -16961,7 +16948,7 @@
         <v>39</v>
       </c>
       <c r="I344" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
@@ -17718,7 +17705,7 @@
         <v>0</v>
       </c>
       <c r="I373" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.25">
@@ -17747,7 +17734,7 @@
         <v>24</v>
       </c>
       <c r="I374" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.25">
@@ -17958,7 +17945,7 @@
         <v>42</v>
       </c>
       <c r="I382" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
@@ -17987,7 +17974,7 @@
         <v>72</v>
       </c>
       <c r="I383" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
@@ -18042,7 +18029,7 @@
         <v>30</v>
       </c>
       <c r="I385" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.25">
@@ -18123,7 +18110,7 @@
         <v>31</v>
       </c>
       <c r="I388" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.25">
@@ -18334,7 +18321,7 @@
         <v>0</v>
       </c>
       <c r="I396" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.25">
@@ -18565,7 +18552,7 @@
         <v>0</v>
       </c>
       <c r="I404" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.25">
@@ -18652,7 +18639,7 @@
         <v>0</v>
       </c>
       <c r="I407" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.25">
@@ -18681,7 +18668,7 @@
         <v>0</v>
       </c>
       <c r="I408" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.25">
@@ -18710,7 +18697,7 @@
         <v>28</v>
       </c>
       <c r="I409" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.25">
@@ -18739,7 +18726,7 @@
         <v>0</v>
       </c>
       <c r="I410" t="s">
-        <v>1894</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="411" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -18768,7 +18755,7 @@
         <v>1</v>
       </c>
       <c r="I411" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="412" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -18852,7 +18839,7 @@
         <v>0</v>
       </c>
       <c r="I414" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="J414" s="5"/>
     </row>
@@ -18994,7 +18981,7 @@
         <v>19</v>
       </c>
       <c r="I419" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="J419" s="5"/>
     </row>
@@ -19052,7 +19039,7 @@
         <v>0</v>
       </c>
       <c r="I421" s="5" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="J421" s="5"/>
     </row>
@@ -19166,7 +19153,7 @@
         <v>56</v>
       </c>
       <c r="I425" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="J425" s="5"/>
     </row>
@@ -19224,7 +19211,7 @@
         <v>0</v>
       </c>
       <c r="I427" s="5" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="J427" s="5"/>
     </row>
@@ -19254,7 +19241,7 @@
         <v>9</v>
       </c>
       <c r="I428" s="5" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="J428" s="5"/>
     </row>
@@ -19508,7 +19495,7 @@
         <v>0</v>
       </c>
       <c r="I437" s="5" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="J437" s="5"/>
     </row>
@@ -19566,7 +19553,7 @@
         <v>14</v>
       </c>
       <c r="I439" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="J439" s="5"/>
     </row>
@@ -19596,7 +19583,7 @@
         <v>44</v>
       </c>
       <c r="I440" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="J440" s="5"/>
     </row>
@@ -20130,7 +20117,7 @@
         <v>24</v>
       </c>
       <c r="I459" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="J459" s="5"/>
     </row>
@@ -20272,7 +20259,7 @@
         <v>129</v>
       </c>
       <c r="I464" s="5" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="J464" s="5"/>
     </row>
@@ -20414,7 +20401,7 @@
         <v>51</v>
       </c>
       <c r="I469" s="8" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="J469" s="5"/>
     </row>
@@ -20680,7 +20667,7 @@
         <v>0</v>
       </c>
       <c r="I478" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="J478" s="5"/>
     </row>
@@ -20710,7 +20697,7 @@
         <v>0</v>
       </c>
       <c r="I479" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="J479" s="5"/>
     </row>
@@ -20740,7 +20727,7 @@
         <v>0</v>
       </c>
       <c r="I480" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="J480" s="5"/>
     </row>
@@ -20761,7 +20748,7 @@
         <v>1335</v>
       </c>
       <c r="F481" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G481">
         <v>63</v>
@@ -20770,7 +20757,7 @@
         <v>0</v>
       </c>
       <c r="I481" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="J481" s="5"/>
     </row>
@@ -20791,7 +20778,7 @@
         <v>1335</v>
       </c>
       <c r="F482" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G482">
         <v>88</v>
@@ -20800,7 +20787,7 @@
         <v>0</v>
       </c>
       <c r="I482" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="J482" s="5"/>
     </row>
@@ -20821,7 +20808,7 @@
         <v>1335</v>
       </c>
       <c r="F483" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G483">
         <v>58</v>
@@ -20830,7 +20817,7 @@
         <v>0</v>
       </c>
       <c r="I483" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="J483" s="5"/>
     </row>
@@ -20860,7 +20847,7 @@
         <v>0</v>
       </c>
       <c r="I484" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="J484" s="5"/>
     </row>
@@ -20890,7 +20877,7 @@
         <v>0</v>
       </c>
       <c r="I485" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="J485" s="5"/>
     </row>
@@ -20920,7 +20907,7 @@
         <v>0</v>
       </c>
       <c r="I486" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="J486" s="5"/>
     </row>
@@ -20950,7 +20937,7 @@
         <v>24</v>
       </c>
       <c r="I487" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
       <c r="J487" s="5"/>
     </row>
@@ -20980,7 +20967,7 @@
         <v>25</v>
       </c>
       <c r="I488" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
       <c r="J488" s="5"/>
     </row>
@@ -21010,7 +20997,7 @@
         <v>14</v>
       </c>
       <c r="I489" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
       <c r="J489" s="5"/>
     </row>
@@ -21031,7 +21018,7 @@
         <v>1335</v>
       </c>
       <c r="F490" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="G490">
         <v>53</v>
@@ -21040,7 +21027,7 @@
         <v>16</v>
       </c>
       <c r="I490" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
       <c r="J490" s="5"/>
     </row>
@@ -21061,7 +21048,7 @@
         <v>1335</v>
       </c>
       <c r="F491" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="G491">
         <v>68</v>
@@ -21070,7 +21057,7 @@
         <v>26</v>
       </c>
       <c r="I491" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
       <c r="J491" s="5"/>
     </row>
@@ -21091,7 +21078,7 @@
         <v>1335</v>
       </c>
       <c r="F492" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="G492">
         <v>61</v>
@@ -21100,7 +21087,7 @@
         <v>1</v>
       </c>
       <c r="I492" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
       <c r="J492" s="5"/>
     </row>
@@ -21130,7 +21117,7 @@
         <v>3</v>
       </c>
       <c r="I493" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
       <c r="J493" s="5"/>
     </row>
@@ -21160,7 +21147,7 @@
         <v>2</v>
       </c>
       <c r="I494" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
       <c r="J494" s="5"/>
     </row>
@@ -21190,7 +21177,7 @@
         <v>4</v>
       </c>
       <c r="I495" s="15" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
       <c r="J495" s="5"/>
     </row>
@@ -21273,7 +21260,7 @@
         <v>0</v>
       </c>
       <c r="I498" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.25">
@@ -21406,7 +21393,7 @@
         <v>105</v>
       </c>
       <c r="I503" s="1" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.25">
@@ -21877,7 +21864,7 @@
         <v>0</v>
       </c>
       <c r="I521" s="5" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="522" spans="1:9" x14ac:dyDescent="0.25">
@@ -22010,7 +21997,7 @@
         <v>41</v>
       </c>
       <c r="I526" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="527" spans="1:9" x14ac:dyDescent="0.25">
@@ -22065,7 +22052,7 @@
         <v>0</v>
       </c>
       <c r="I528" s="5" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="529" spans="1:9" x14ac:dyDescent="0.25">
@@ -22094,7 +22081,7 @@
         <v>0</v>
       </c>
       <c r="I529" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="530" spans="1:9" x14ac:dyDescent="0.25">
@@ -22149,7 +22136,7 @@
         <v>73</v>
       </c>
       <c r="I531" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.25">
@@ -22334,7 +22321,7 @@
         <v>67</v>
       </c>
       <c r="I538" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="539" spans="1:9" x14ac:dyDescent="0.25">
@@ -22545,7 +22532,7 @@
         <v>72</v>
       </c>
       <c r="I546" s="1" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.25">
@@ -22600,7 +22587,7 @@
         <v>119</v>
       </c>
       <c r="I548" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="549" spans="1:9" x14ac:dyDescent="0.25">
@@ -22629,7 +22616,7 @@
         <v>70</v>
       </c>
       <c r="I549" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.25">
@@ -22658,7 +22645,7 @@
         <v>91</v>
       </c>
       <c r="I550" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="551" spans="1:9" x14ac:dyDescent="0.25">
@@ -22765,7 +22752,7 @@
         <v>63</v>
       </c>
       <c r="I554" s="1" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.25">
@@ -23141,7 +23128,7 @@
         <v>0</v>
       </c>
       <c r="I568" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.25">
@@ -23170,7 +23157,7 @@
         <v>0</v>
       </c>
       <c r="I569" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.25">
@@ -23199,7 +23186,7 @@
         <v>0</v>
       </c>
       <c r="I570" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.25">
@@ -23219,7 +23206,7 @@
         <v>1538</v>
       </c>
       <c r="F571" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G571">
         <v>55</v>
@@ -23228,7 +23215,7 @@
         <v>0</v>
       </c>
       <c r="I571" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.25">
@@ -23248,7 +23235,7 @@
         <v>1538</v>
       </c>
       <c r="F572" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G572">
         <v>68</v>
@@ -23257,7 +23244,7 @@
         <v>0</v>
       </c>
       <c r="I572" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.25">
@@ -23277,7 +23264,7 @@
         <v>1538</v>
       </c>
       <c r="F573" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G573">
         <v>73</v>
@@ -23286,7 +23273,7 @@
         <v>0</v>
       </c>
       <c r="I573" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.25">
@@ -23315,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="I574" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.25">
@@ -23344,7 +23331,7 @@
         <v>0</v>
       </c>
       <c r="I575" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="576" spans="1:9" x14ac:dyDescent="0.25">
@@ -23373,7 +23360,7 @@
         <v>0</v>
       </c>
       <c r="I576" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.25">
@@ -23402,7 +23389,7 @@
         <v>33</v>
       </c>
       <c r="I577" s="16" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="578" spans="1:9" x14ac:dyDescent="0.25">
@@ -23431,7 +23418,7 @@
         <v>34</v>
       </c>
       <c r="I578" s="16" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.25">
@@ -23460,7 +23447,7 @@
         <v>16</v>
       </c>
       <c r="I579" s="16" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.25">
@@ -23480,7 +23467,7 @@
         <v>1538</v>
       </c>
       <c r="F580" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="G580">
         <v>65</v>
@@ -23489,7 +23476,7 @@
         <v>23</v>
       </c>
       <c r="I580" s="16" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.25">
@@ -23509,7 +23496,7 @@
         <v>1538</v>
       </c>
       <c r="F581" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="G581">
         <v>70</v>
@@ -23518,7 +23505,7 @@
         <v>30</v>
       </c>
       <c r="I581" s="16" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.25">
@@ -23538,7 +23525,7 @@
         <v>1538</v>
       </c>
       <c r="F582" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="G582">
         <v>57</v>
@@ -23547,7 +23534,7 @@
         <v>4</v>
       </c>
       <c r="I582" s="16" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.25">
@@ -23576,7 +23563,7 @@
         <v>4</v>
       </c>
       <c r="I583" s="16" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="584" spans="1:9" x14ac:dyDescent="0.25">
@@ -23605,7 +23592,7 @@
         <v>4</v>
       </c>
       <c r="I584" s="16" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.25">
@@ -23634,7 +23621,7 @@
         <v>8</v>
       </c>
       <c r="I585" s="16" t="s">
-        <v>1861</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="586" spans="1:9" x14ac:dyDescent="0.25">
@@ -23668,7 +23655,7 @@
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" s="17" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="B587" s="5" t="s">
         <v>1831</v>
@@ -23692,12 +23679,12 @@
         <v>333</v>
       </c>
       <c r="I587" s="19" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" s="17" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="B588" s="5" t="s">
         <v>1831</v>
@@ -23721,7 +23708,7 @@
         <v>386</v>
       </c>
       <c r="I588" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.25">
@@ -23750,12 +23737,12 @@
         <v>0</v>
       </c>
       <c r="I589" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" s="17" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="B590" s="5" t="s">
         <v>1831</v>
@@ -23779,7 +23766,7 @@
         <v>6</v>
       </c>
       <c r="I590" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.25">
@@ -23808,7 +23795,7 @@
         <v>0</v>
       </c>
       <c r="I591" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.25">
@@ -23837,12 +23824,12 @@
         <v>0</v>
       </c>
       <c r="I592" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" s="17" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="B593" t="s">
         <v>1846</v>
@@ -23857,7 +23844,7 @@
         <v>1796</v>
       </c>
       <c r="F593" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="G593">
         <v>270</v>
@@ -23866,7 +23853,7 @@
         <v>0</v>
       </c>
       <c r="I593" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="594" spans="1:9" x14ac:dyDescent="0.25">
@@ -23886,7 +23873,7 @@
         <v>1796</v>
       </c>
       <c r="F594" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="G594" s="1">
         <v>0</v>
@@ -23895,12 +23882,12 @@
         <v>0</v>
       </c>
       <c r="I594" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" s="17" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="B595" t="s">
         <v>1809</v>
@@ -23915,7 +23902,7 @@
         <v>1796</v>
       </c>
       <c r="F595" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="G595">
         <v>187</v>
@@ -23924,12 +23911,12 @@
         <v>0</v>
       </c>
       <c r="I595" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" s="20" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="B596" s="5" t="s">
         <v>1795</v>
@@ -23944,7 +23931,7 @@
         <v>1796</v>
       </c>
       <c r="F596" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="G596">
         <v>201</v>
@@ -23953,12 +23940,12 @@
         <v>0</v>
       </c>
       <c r="I596" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" s="17" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="B597" t="s">
         <v>1808</v>
@@ -23982,12 +23969,12 @@
         <v>0</v>
       </c>
       <c r="I597" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" s="17" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="B598" t="s">
         <v>1849</v>
@@ -24011,12 +23998,12 @@
         <v>0</v>
       </c>
       <c r="I598" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" s="17" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="B599" t="s">
         <v>1799</v>
@@ -24040,12 +24027,12 @@
         <v>0</v>
       </c>
       <c r="I599" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" s="17" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="B600" t="s">
         <v>1806</v>
@@ -24069,12 +24056,12 @@
         <v>0</v>
       </c>
       <c r="I600" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" s="17" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="B601" t="s">
         <v>1807</v>
@@ -24103,7 +24090,7 @@
     </row>
     <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" s="17" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="B602" t="s">
         <v>1802</v>
@@ -24161,7 +24148,7 @@
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" s="17" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="B604" t="s">
         <v>1815</v>
@@ -24176,7 +24163,7 @@
         <v>1796</v>
       </c>
       <c r="F604" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G604" s="1">
         <v>0</v>
@@ -24185,12 +24172,12 @@
         <v>0</v>
       </c>
       <c r="I604" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" s="17" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="B605" t="s">
         <v>1817</v>
@@ -24205,7 +24192,7 @@
         <v>1796</v>
       </c>
       <c r="F605" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G605">
         <v>193</v>
@@ -24214,12 +24201,12 @@
         <v>0</v>
       </c>
       <c r="I605" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" s="17" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="B606" t="s">
         <v>1834</v>
@@ -24234,7 +24221,7 @@
         <v>1796</v>
       </c>
       <c r="F606" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G606">
         <v>199</v>
@@ -24243,12 +24230,12 @@
         <v>0</v>
       </c>
       <c r="I606" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" s="17" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="B607" t="s">
         <v>1800</v>
@@ -24263,7 +24250,7 @@
         <v>1796</v>
       </c>
       <c r="F607" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="G607">
         <v>139</v>
@@ -24272,7 +24259,7 @@
         <v>0</v>
       </c>
       <c r="I607" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="608" spans="1:9" x14ac:dyDescent="0.25">
@@ -24306,7 +24293,7 @@
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" s="17" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="B609" t="s">
         <v>1816</v>
@@ -24330,12 +24317,12 @@
         <v>1024</v>
       </c>
       <c r="I609" s="16" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" s="17" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="B610" t="s">
         <v>1816</v>
@@ -24359,12 +24346,12 @@
         <v>113</v>
       </c>
       <c r="I610" s="16" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" s="17" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="B611" t="s">
         <v>1816</v>
@@ -24388,12 +24375,12 @@
         <v>971</v>
       </c>
       <c r="I611" s="16" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" s="17" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="B612" t="s">
         <v>1816</v>
@@ -24417,7 +24404,7 @@
         <v>829</v>
       </c>
       <c r="I612" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="613" spans="1:9" x14ac:dyDescent="0.25">
@@ -24446,7 +24433,7 @@
         <v>0</v>
       </c>
       <c r="I613" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.25">
@@ -24475,7 +24462,7 @@
         <v>0</v>
       </c>
       <c r="I614" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.25">
@@ -24504,12 +24491,12 @@
         <v>0</v>
       </c>
       <c r="I615" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" s="17" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="B616" t="s">
         <v>1838</v>
@@ -24524,7 +24511,7 @@
         <v>1796</v>
       </c>
       <c r="F616" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="G616">
         <v>337</v>
@@ -24538,7 +24525,7 @@
     </row>
     <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" s="17" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="B617" t="s">
         <v>1805</v>
@@ -24553,7 +24540,7 @@
         <v>1796</v>
       </c>
       <c r="F617" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="G617">
         <v>403</v>
@@ -24567,7 +24554,7 @@
     </row>
     <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" s="17" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B618" t="s">
         <v>1847</v>
@@ -24582,7 +24569,7 @@
         <v>1796</v>
       </c>
       <c r="F618" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="G618">
         <v>481</v>
@@ -24596,7 +24583,7 @@
     </row>
     <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" s="17" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="B619" t="s">
         <v>1844</v>
@@ -24611,7 +24598,7 @@
         <v>1796</v>
       </c>
       <c r="F619" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="G619">
         <v>737</v>
@@ -24625,7 +24612,7 @@
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" s="17" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B620" t="s">
         <v>1829</v>
@@ -24640,7 +24627,7 @@
         <v>1796</v>
       </c>
       <c r="F620" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="G620">
         <v>286</v>
@@ -24654,7 +24641,7 @@
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" s="17" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="B621" t="s">
         <v>1820</v>
@@ -24669,7 +24656,7 @@
         <v>1796</v>
       </c>
       <c r="F621" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="G621" s="1">
         <v>0</v>
@@ -24678,7 +24665,7 @@
         <v>0</v>
       </c>
       <c r="I621" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="622" spans="1:9" x14ac:dyDescent="0.25">
@@ -24707,12 +24694,12 @@
         <v>6</v>
       </c>
       <c r="I622" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" s="17" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B623" t="s">
         <v>1818</v>
@@ -24736,12 +24723,12 @@
         <v>4</v>
       </c>
       <c r="I623" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" s="17" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="B624" t="s">
         <v>1818</v>
@@ -24765,12 +24752,12 @@
         <v>402</v>
       </c>
       <c r="I624" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" s="17" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B625" t="s">
         <v>1818</v>
@@ -24794,7 +24781,7 @@
         <v>0</v>
       </c>
       <c r="I625" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="626" spans="1:9" x14ac:dyDescent="0.25">
@@ -24802,7 +24789,7 @@
         <v>739</v>
       </c>
       <c r="B626" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C626" t="s">
         <v>300</v>
@@ -24823,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="I626" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="627" spans="1:9" x14ac:dyDescent="0.25">
@@ -24831,7 +24818,7 @@
         <v>1821</v>
       </c>
       <c r="B627" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C627" t="s">
         <v>304</v>
@@ -24852,7 +24839,7 @@
         <v>0</v>
       </c>
       <c r="I627" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.25">
@@ -24860,7 +24847,7 @@
         <v>1841</v>
       </c>
       <c r="B628" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C628" t="s">
         <v>308</v>
@@ -24881,7 +24868,7 @@
         <v>0</v>
       </c>
       <c r="I628" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.25">
@@ -24889,7 +24876,7 @@
         <v>1824</v>
       </c>
       <c r="B629" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C629" t="s">
         <v>312</v>
@@ -24910,7 +24897,7 @@
         <v>0</v>
       </c>
       <c r="I629" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="630" spans="1:9" x14ac:dyDescent="0.25">
@@ -24918,7 +24905,7 @@
         <v>1827</v>
       </c>
       <c r="B630" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C630" t="s">
         <v>1828</v>
@@ -24939,15 +24926,15 @@
         <v>0</v>
       </c>
       <c r="I630" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" s="17" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="B631" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C631" t="s">
         <v>1835</v>
@@ -24968,15 +24955,15 @@
         <v>37</v>
       </c>
       <c r="I631" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" s="17" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="B632" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C632" t="s">
         <v>172</v>
@@ -24997,7 +24984,7 @@
         <v>278</v>
       </c>
       <c r="I632" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.25">
@@ -25005,7 +24992,7 @@
         <v>1287</v>
       </c>
       <c r="B633" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C633" t="s">
         <v>839</v>
@@ -25026,7 +25013,7 @@
         <v>1371</v>
       </c>
       <c r="I633" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="634" spans="1:9" x14ac:dyDescent="0.25">
@@ -25034,7 +25021,7 @@
         <v>1837</v>
       </c>
       <c r="B634" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C634" t="s">
         <v>315</v>
@@ -25055,7 +25042,7 @@
         <v>0</v>
       </c>
       <c r="I634" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="635" spans="1:9" x14ac:dyDescent="0.25">
@@ -25063,7 +25050,7 @@
         <v>1812</v>
       </c>
       <c r="B635" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C635" t="s">
         <v>1813</v>
@@ -25084,7 +25071,7 @@
         <v>0</v>
       </c>
       <c r="I635" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.25">
@@ -25092,7 +25079,7 @@
         <v>1845</v>
       </c>
       <c r="B636" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C636" t="s">
         <v>345</v>
@@ -25113,7 +25100,7 @@
         <v>0</v>
       </c>
       <c r="I636" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="637" spans="1:9" x14ac:dyDescent="0.25">
@@ -25121,7 +25108,7 @@
         <v>1797</v>
       </c>
       <c r="B637" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C637" t="s">
         <v>349</v>
@@ -25142,15 +25129,15 @@
         <v>0</v>
       </c>
       <c r="I637" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" s="17" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="B638" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C638" t="s">
         <v>353</v>
@@ -25171,15 +25158,15 @@
         <v>883</v>
       </c>
       <c r="I638" s="16" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" s="17" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="B639" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="E639" t="s">
         <v>1796</v>
@@ -25194,15 +25181,15 @@
         <v>75</v>
       </c>
       <c r="I639" s="18" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" s="17" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B640" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="E640" t="s">
         <v>1796</v>
@@ -25217,15 +25204,15 @@
         <v>44</v>
       </c>
       <c r="I640" s="18" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" s="17" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B641" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="E641" t="s">
         <v>1796</v>
@@ -25240,15 +25227,15 @@
         <v>406</v>
       </c>
       <c r="I641" s="18" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" s="17" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B642" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="E642" t="s">
         <v>1796</v>
@@ -25263,15 +25250,15 @@
         <v>99</v>
       </c>
       <c r="I642" s="18" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" s="17" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="B643" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="E643" t="s">
         <v>1796</v>
@@ -25286,15 +25273,15 @@
         <v>518</v>
       </c>
       <c r="I643" s="18" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" s="17" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B644" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="E644" t="s">
         <v>1796</v>
@@ -25309,15 +25296,15 @@
         <v>183</v>
       </c>
       <c r="I644" s="18" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" s="17" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B645" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="E645" t="s">
         <v>1796</v>
@@ -25332,7 +25319,7 @@
         <v>383</v>
       </c>
       <c r="I645" s="18" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
     </row>
   </sheetData>

--- a/metadata/C3H10_10X_Metadata.xlsx
+++ b/metadata/C3H10_10X_Metadata.xlsx
@@ -1,37 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20406"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\TF-seq\metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\updeplanas2.epfl.ch\DeplanckeNAS2\TF-seq\Wangjie\TF-seq_GitHub\TF-seq\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544F7C1D-62E6-47C3-9648-C6C8D7D22C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D53707-E8BC-4CB8-8AAB-43DF80E2A947}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C3H10_10X_Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4088" uniqueCount="1990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4089" uniqueCount="1991">
   <si>
     <t>TF_name</t>
   </si>
@@ -6755,6 +6744,9 @@
       </rPr>
       <t xml:space="preserve"> Myo_ref</t>
     </r>
+  </si>
+  <si>
+    <t>Renamed Tada2a</t>
   </si>
 </sst>
 </file>
@@ -6900,6 +6892,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -7633,21 +7626,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L645"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -7676,7 +7669,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -7705,7 +7698,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -7734,7 +7727,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -7763,7 +7756,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7792,7 +7785,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -7821,7 +7814,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -7850,7 +7843,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -7879,7 +7872,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -7908,7 +7901,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -7945,7 +7938,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -7974,7 +7967,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -8003,7 +7996,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -8032,7 +8025,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -8061,7 +8054,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -8090,7 +8083,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -8116,7 +8109,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>65</v>
       </c>
@@ -8142,7 +8135,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -8168,7 +8161,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>71</v>
       </c>
@@ -8194,7 +8187,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -8220,7 +8213,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>77</v>
       </c>
@@ -8246,7 +8239,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>80</v>
       </c>
@@ -8272,7 +8265,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>83</v>
       </c>
@@ -8298,7 +8291,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>86</v>
       </c>
@@ -8324,7 +8317,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>89</v>
       </c>
@@ -8350,7 +8343,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>92</v>
       </c>
@@ -8376,7 +8369,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>95</v>
       </c>
@@ -8402,7 +8395,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -8428,7 +8421,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>101</v>
       </c>
@@ -8454,7 +8447,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>104</v>
       </c>
@@ -8480,7 +8473,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>107</v>
       </c>
@@ -8506,7 +8499,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>110</v>
       </c>
@@ -8532,7 +8525,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>113</v>
       </c>
@@ -8558,7 +8551,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>116</v>
       </c>
@@ -8584,7 +8577,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -8610,7 +8603,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>122</v>
       </c>
@@ -8636,7 +8629,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -8662,7 +8655,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>128</v>
       </c>
@@ -8688,7 +8681,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>131</v>
       </c>
@@ -8714,7 +8707,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>134</v>
       </c>
@@ -8740,7 +8733,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>137</v>
       </c>
@@ -8766,7 +8759,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>140</v>
       </c>
@@ -8792,7 +8785,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>143</v>
       </c>
@@ -8821,7 +8814,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>146</v>
       </c>
@@ -8847,7 +8840,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>149</v>
       </c>
@@ -8873,7 +8866,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>152</v>
       </c>
@@ -8899,7 +8892,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>155</v>
       </c>
@@ -8925,7 +8918,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>158</v>
       </c>
@@ -8951,7 +8944,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>161</v>
       </c>
@@ -8977,7 +8970,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>164</v>
       </c>
@@ -9003,7 +8996,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>167</v>
       </c>
@@ -9029,7 +9022,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>170</v>
       </c>
@@ -9055,7 +9048,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>5</v>
       </c>
@@ -9084,7 +9077,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>10</v>
       </c>
@@ -9113,7 +9106,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>14</v>
       </c>
@@ -9142,7 +9135,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -9171,7 +9164,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -9200,7 +9193,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -9229,7 +9222,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>30</v>
       </c>
@@ -9258,7 +9251,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>34</v>
       </c>
@@ -9287,7 +9280,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>38</v>
       </c>
@@ -9316,7 +9309,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>42</v>
       </c>
@@ -9345,7 +9338,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>46</v>
       </c>
@@ -9374,7 +9367,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>175</v>
       </c>
@@ -9403,7 +9396,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>50</v>
       </c>
@@ -9432,7 +9425,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>54</v>
       </c>
@@ -9461,7 +9454,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>58</v>
       </c>
@@ -9490,7 +9483,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>179</v>
       </c>
@@ -9516,7 +9509,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>183</v>
       </c>
@@ -9545,7 +9538,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>89</v>
       </c>
@@ -9571,7 +9564,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>190</v>
       </c>
@@ -9597,7 +9590,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -9623,7 +9616,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>198</v>
       </c>
@@ -9649,7 +9642,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>202</v>
       </c>
@@ -9675,7 +9668,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>206</v>
       </c>
@@ -9704,7 +9697,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>210</v>
       </c>
@@ -9730,7 +9723,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>214</v>
       </c>
@@ -9756,7 +9749,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>218</v>
       </c>
@@ -9782,7 +9775,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>222</v>
       </c>
@@ -9811,7 +9804,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>226</v>
       </c>
@@ -9840,7 +9833,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>230</v>
       </c>
@@ -9869,7 +9862,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>234</v>
       </c>
@@ -9895,7 +9888,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>238</v>
       </c>
@@ -9921,7 +9914,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>242</v>
       </c>
@@ -9947,7 +9940,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>246</v>
       </c>
@@ -9973,7 +9966,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>250</v>
       </c>
@@ -9999,7 +9992,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>254</v>
       </c>
@@ -10025,7 +10018,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>258</v>
       </c>
@@ -10054,7 +10047,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>262</v>
       </c>
@@ -10083,7 +10076,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>266</v>
       </c>
@@ -10112,7 +10105,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>270</v>
       </c>
@@ -10138,7 +10131,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>274</v>
       </c>
@@ -10167,7 +10160,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>278</v>
       </c>
@@ -10193,7 +10186,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>282</v>
       </c>
@@ -10222,7 +10215,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>286</v>
       </c>
@@ -10251,7 +10244,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>290</v>
       </c>
@@ -10277,7 +10270,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>294</v>
       </c>
@@ -10303,7 +10296,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>298</v>
       </c>
@@ -10332,7 +10325,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>302</v>
       </c>
@@ -10361,7 +10354,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>306</v>
       </c>
@@ -10390,7 +10383,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>310</v>
       </c>
@@ -10416,7 +10409,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>152</v>
       </c>
@@ -10445,7 +10438,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>317</v>
       </c>
@@ -10474,7 +10467,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>321</v>
       </c>
@@ -10500,7 +10493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>325</v>
       </c>
@@ -10526,7 +10519,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>86</v>
       </c>
@@ -10555,7 +10548,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>77</v>
       </c>
@@ -10581,7 +10574,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>335</v>
       </c>
@@ -10610,7 +10603,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>339</v>
       </c>
@@ -10639,7 +10632,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>343</v>
       </c>
@@ -10668,7 +10661,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>347</v>
       </c>
@@ -10697,7 +10690,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>351</v>
       </c>
@@ -10723,7 +10716,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>355</v>
       </c>
@@ -10749,7 +10742,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>359</v>
       </c>
@@ -10775,7 +10768,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>363</v>
       </c>
@@ -10801,7 +10794,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>367</v>
       </c>
@@ -10830,7 +10823,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>371</v>
       </c>
@@ -10856,7 +10849,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>375</v>
       </c>
@@ -10885,7 +10878,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>379</v>
       </c>
@@ -10911,7 +10904,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>383</v>
       </c>
@@ -10940,7 +10933,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>387</v>
       </c>
@@ -10966,7 +10959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>391</v>
       </c>
@@ -10995,7 +10988,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>395</v>
       </c>
@@ -11021,7 +11014,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>62</v>
       </c>
@@ -11050,7 +11043,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>402</v>
       </c>
@@ -11079,7 +11072,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>406</v>
       </c>
@@ -11105,7 +11098,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>410</v>
       </c>
@@ -11131,7 +11124,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>414</v>
       </c>
@@ -11157,7 +11150,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>418</v>
       </c>
@@ -11183,7 +11176,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>422</v>
       </c>
@@ -11209,7 +11202,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>426</v>
       </c>
@@ -11235,7 +11228,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>430</v>
       </c>
@@ -11261,7 +11254,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>434</v>
       </c>
@@ -11287,7 +11280,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>438</v>
       </c>
@@ -11316,7 +11309,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>442</v>
       </c>
@@ -11342,7 +11335,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>446</v>
       </c>
@@ -11368,7 +11361,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>450</v>
       </c>
@@ -11397,7 +11390,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>454</v>
       </c>
@@ -11423,7 +11416,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>458</v>
       </c>
@@ -11450,7 +11443,7 @@
       </c>
       <c r="I139" s="3"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>463</v>
       </c>
@@ -11476,7 +11469,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>467</v>
       </c>
@@ -11502,7 +11495,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>471</v>
       </c>
@@ -11531,7 +11524,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>475</v>
       </c>
@@ -11560,7 +11553,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>479</v>
       </c>
@@ -11589,7 +11582,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>483</v>
       </c>
@@ -11615,7 +11608,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>487</v>
       </c>
@@ -11641,7 +11634,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>491</v>
       </c>
@@ -11667,7 +11660,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>495</v>
       </c>
@@ -11693,7 +11686,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>499</v>
       </c>
@@ -11722,7 +11715,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>503</v>
       </c>
@@ -11748,7 +11741,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>507</v>
       </c>
@@ -11774,7 +11767,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>511</v>
       </c>
@@ -11800,7 +11793,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>515</v>
       </c>
@@ -11826,7 +11819,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>519</v>
       </c>
@@ -11852,7 +11845,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>523</v>
       </c>
@@ -11878,7 +11871,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>527</v>
       </c>
@@ -11904,7 +11897,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>531</v>
       </c>
@@ -11930,7 +11923,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>535</v>
       </c>
@@ -11956,7 +11949,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>539</v>
       </c>
@@ -11982,7 +11975,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>543</v>
       </c>
@@ -12008,7 +12001,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>547</v>
       </c>
@@ -12037,7 +12030,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>551</v>
       </c>
@@ -12063,7 +12056,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>555</v>
       </c>
@@ -12089,7 +12082,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>559</v>
       </c>
@@ -12115,7 +12108,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>563</v>
       </c>
@@ -12141,7 +12134,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>567</v>
       </c>
@@ -12167,7 +12160,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>571</v>
       </c>
@@ -12193,7 +12186,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>575</v>
       </c>
@@ -12219,7 +12212,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>579</v>
       </c>
@@ -12245,7 +12238,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>583</v>
       </c>
@@ -12271,7 +12264,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>587</v>
       </c>
@@ -12297,7 +12290,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>591</v>
       </c>
@@ -12323,7 +12316,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>595</v>
       </c>
@@ -12349,7 +12342,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>599</v>
       </c>
@@ -12375,7 +12368,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>603</v>
       </c>
@@ -12401,7 +12394,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>607</v>
       </c>
@@ -12427,7 +12420,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>611</v>
       </c>
@@ -12453,7 +12446,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>615</v>
       </c>
@@ -12479,7 +12472,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>619</v>
       </c>
@@ -12505,7 +12498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>623</v>
       </c>
@@ -12531,7 +12524,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>627</v>
       </c>
@@ -12557,7 +12550,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>631</v>
       </c>
@@ -12583,7 +12576,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>635</v>
       </c>
@@ -12609,7 +12602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>639</v>
       </c>
@@ -12635,7 +12628,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>643</v>
       </c>
@@ -12661,7 +12654,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>647</v>
       </c>
@@ -12687,7 +12680,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>651</v>
       </c>
@@ -12713,7 +12706,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>655</v>
       </c>
@@ -12739,7 +12732,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>659</v>
       </c>
@@ -12765,7 +12758,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>663</v>
       </c>
@@ -12791,7 +12784,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>667</v>
       </c>
@@ -12817,7 +12810,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>671</v>
       </c>
@@ -12846,7 +12839,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>675</v>
       </c>
@@ -12872,7 +12865,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>679</v>
       </c>
@@ -12898,7 +12891,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>683</v>
       </c>
@@ -12924,7 +12917,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>687</v>
       </c>
@@ -12950,7 +12943,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>691</v>
       </c>
@@ -12979,7 +12972,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>695</v>
       </c>
@@ -13005,7 +12998,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>699</v>
       </c>
@@ -13031,7 +13024,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>703</v>
       </c>
@@ -13057,7 +13050,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>707</v>
       </c>
@@ -13083,7 +13076,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>711</v>
       </c>
@@ -13109,7 +13102,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>715</v>
       </c>
@@ -13135,7 +13128,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>719</v>
       </c>
@@ -13161,7 +13154,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>723</v>
       </c>
@@ -13187,7 +13180,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>727</v>
       </c>
@@ -13213,7 +13206,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>731</v>
       </c>
@@ -13239,7 +13232,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>735</v>
       </c>
@@ -13265,7 +13258,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>5</v>
       </c>
@@ -13294,7 +13287,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>10</v>
       </c>
@@ -13323,7 +13316,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>14</v>
       </c>
@@ -13352,7 +13345,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -13381,7 +13374,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>22</v>
       </c>
@@ -13410,7 +13403,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>26</v>
       </c>
@@ -13439,7 +13432,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>30</v>
       </c>
@@ -13468,7 +13461,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>34</v>
       </c>
@@ -13497,7 +13490,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>38</v>
       </c>
@@ -13526,7 +13519,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>42</v>
       </c>
@@ -13555,7 +13548,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>46</v>
       </c>
@@ -13584,7 +13577,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>175</v>
       </c>
@@ -13613,7 +13606,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>50</v>
       </c>
@@ -13642,7 +13635,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>54</v>
       </c>
@@ -13671,7 +13664,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>58</v>
       </c>
@@ -13700,7 +13693,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>170</v>
       </c>
@@ -13726,7 +13719,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>740</v>
       </c>
@@ -13755,7 +13748,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>128</v>
       </c>
@@ -13781,7 +13774,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>134</v>
       </c>
@@ -13807,7 +13800,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>741</v>
       </c>
@@ -13836,7 +13829,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>744</v>
       </c>
@@ -13862,7 +13855,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>746</v>
       </c>
@@ -13888,7 +13881,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>748</v>
       </c>
@@ -13914,7 +13907,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>750</v>
       </c>
@@ -13940,7 +13933,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>754</v>
       </c>
@@ -13966,7 +13959,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>758</v>
       </c>
@@ -13992,7 +13985,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>762</v>
       </c>
@@ -14018,7 +14011,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>766</v>
       </c>
@@ -14047,7 +14040,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>770</v>
       </c>
@@ -14073,7 +14066,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>774</v>
       </c>
@@ -14099,7 +14092,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>778</v>
       </c>
@@ -14128,7 +14121,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>782</v>
       </c>
@@ -14157,7 +14150,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>786</v>
       </c>
@@ -14183,7 +14176,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>790</v>
       </c>
@@ -14209,7 +14202,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>794</v>
       </c>
@@ -14235,7 +14228,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>798</v>
       </c>
@@ -14261,7 +14254,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>802</v>
       </c>
@@ -14287,7 +14280,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>806</v>
       </c>
@@ -14313,7 +14306,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>810</v>
       </c>
@@ -14339,7 +14332,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>83</v>
       </c>
@@ -14365,7 +14358,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>817</v>
       </c>
@@ -14391,7 +14384,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>821</v>
       </c>
@@ -14417,7 +14410,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>825</v>
       </c>
@@ -14443,7 +14436,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>829</v>
       </c>
@@ -14469,7 +14462,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>833</v>
       </c>
@@ -14498,7 +14491,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>837</v>
       </c>
@@ -14527,7 +14520,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>841</v>
       </c>
@@ -14553,7 +14546,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>845</v>
       </c>
@@ -14579,7 +14572,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>849</v>
       </c>
@@ -14605,7 +14598,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>853</v>
       </c>
@@ -14631,7 +14624,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>857</v>
       </c>
@@ -14657,7 +14650,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>861</v>
       </c>
@@ -14683,7 +14676,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>865</v>
       </c>
@@ -14709,7 +14702,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>869</v>
       </c>
@@ -14735,7 +14728,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>873</v>
       </c>
@@ -14761,7 +14754,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>101</v>
       </c>
@@ -14790,7 +14783,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>880</v>
       </c>
@@ -14816,7 +14809,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>80</v>
       </c>
@@ -14842,7 +14835,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>887</v>
       </c>
@@ -14868,7 +14861,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>891</v>
       </c>
@@ -14894,7 +14887,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>895</v>
       </c>
@@ -14920,7 +14913,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>899</v>
       </c>
@@ -14946,7 +14939,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>903</v>
       </c>
@@ -14972,7 +14965,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>907</v>
       </c>
@@ -14998,7 +14991,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>911</v>
       </c>
@@ -15024,7 +15017,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>915</v>
       </c>
@@ -15050,7 +15043,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>919</v>
       </c>
@@ -15076,7 +15069,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>923</v>
       </c>
@@ -15102,7 +15095,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>927</v>
       </c>
@@ -15128,7 +15121,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>931</v>
       </c>
@@ -15154,7 +15147,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>935</v>
       </c>
@@ -15183,7 +15176,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>939</v>
       </c>
@@ -15209,7 +15202,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>943</v>
       </c>
@@ -15235,7 +15228,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>947</v>
       </c>
@@ -15261,7 +15254,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>951</v>
       </c>
@@ -15287,7 +15280,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>955</v>
       </c>
@@ -15313,7 +15306,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>959</v>
       </c>
@@ -15339,7 +15332,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>963</v>
       </c>
@@ -15368,7 +15361,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>967</v>
       </c>
@@ -15394,7 +15387,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>971</v>
       </c>
@@ -15420,7 +15413,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>975</v>
       </c>
@@ -15446,7 +15439,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>979</v>
       </c>
@@ -15472,7 +15465,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>983</v>
       </c>
@@ -15498,7 +15491,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>986</v>
       </c>
@@ -15524,7 +15517,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>990</v>
       </c>
@@ -15550,7 +15543,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>994</v>
       </c>
@@ -15576,7 +15569,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>998</v>
       </c>
@@ -15605,7 +15598,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1002</v>
       </c>
@@ -15631,7 +15624,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1006</v>
       </c>
@@ -15657,7 +15650,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>1010</v>
       </c>
@@ -15683,7 +15676,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1014</v>
       </c>
@@ -15709,7 +15702,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1018</v>
       </c>
@@ -15735,7 +15728,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1022</v>
       </c>
@@ -15761,7 +15754,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1026</v>
       </c>
@@ -15787,7 +15780,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1030</v>
       </c>
@@ -15813,7 +15806,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>5</v>
       </c>
@@ -15842,7 +15835,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>10</v>
       </c>
@@ -15871,7 +15864,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>14</v>
       </c>
@@ -15900,7 +15893,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>18</v>
       </c>
@@ -15929,7 +15922,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>22</v>
       </c>
@@ -15958,7 +15951,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>26</v>
       </c>
@@ -15987,7 +15980,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>30</v>
       </c>
@@ -16016,7 +16009,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>34</v>
       </c>
@@ -16045,7 +16038,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>38</v>
       </c>
@@ -16074,7 +16067,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>42</v>
       </c>
@@ -16103,7 +16096,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>46</v>
       </c>
@@ -16132,7 +16125,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>175</v>
       </c>
@@ -16161,7 +16154,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>50</v>
       </c>
@@ -16190,7 +16183,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>54</v>
       </c>
@@ -16219,7 +16212,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>58</v>
       </c>
@@ -16248,7 +16241,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>170</v>
       </c>
@@ -16274,7 +16267,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>740</v>
       </c>
@@ -16303,7 +16296,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>128</v>
       </c>
@@ -16329,7 +16322,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>134</v>
       </c>
@@ -16355,7 +16348,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
         <v>1034</v>
       </c>
@@ -16384,7 +16377,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>1037</v>
       </c>
@@ -16413,7 +16406,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>1039</v>
       </c>
@@ -16439,7 +16432,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>1043</v>
       </c>
@@ -16465,7 +16458,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>1045</v>
       </c>
@@ -16491,7 +16484,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>1049</v>
       </c>
@@ -16517,7 +16510,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>1053</v>
       </c>
@@ -16543,7 +16536,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>1057</v>
       </c>
@@ -16569,7 +16562,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>1061</v>
       </c>
@@ -16595,7 +16588,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>1065</v>
       </c>
@@ -16624,7 +16617,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>1069</v>
       </c>
@@ -16650,7 +16643,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>1073</v>
       </c>
@@ -16676,7 +16669,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1077</v>
       </c>
@@ -16702,7 +16695,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1081</v>
       </c>
@@ -16728,7 +16721,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1085</v>
       </c>
@@ -16757,7 +16750,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1089</v>
       </c>
@@ -16783,7 +16776,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1093</v>
       </c>
@@ -16809,7 +16802,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1097</v>
       </c>
@@ -16838,7 +16831,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1101</v>
       </c>
@@ -16867,7 +16860,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1105</v>
       </c>
@@ -16896,7 +16889,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>1109</v>
       </c>
@@ -16921,8 +16914,11 @@
       <c r="H343">
         <v>62</v>
       </c>
-    </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I343" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1113</v>
       </c>
@@ -16951,7 +16947,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1117</v>
       </c>
@@ -16977,7 +16973,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>1121</v>
       </c>
@@ -17003,7 +16999,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1125</v>
       </c>
@@ -17029,7 +17025,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>1129</v>
       </c>
@@ -17055,7 +17051,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>1133</v>
       </c>
@@ -17081,7 +17077,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>1137</v>
       </c>
@@ -17107,7 +17103,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1141</v>
       </c>
@@ -17133,7 +17129,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1145</v>
       </c>
@@ -17159,7 +17155,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>1149</v>
       </c>
@@ -17185,7 +17181,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>1153</v>
       </c>
@@ -17211,7 +17207,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1157</v>
       </c>
@@ -17237,7 +17233,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>1161</v>
       </c>
@@ -17263,7 +17259,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>1165</v>
       </c>
@@ -17289,7 +17285,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>1169</v>
       </c>
@@ -17315,7 +17311,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>1173</v>
       </c>
@@ -17341,7 +17337,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>1177</v>
       </c>
@@ -17367,7 +17363,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>1181</v>
       </c>
@@ -17393,7 +17389,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>1185</v>
       </c>
@@ -17419,7 +17415,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>1189</v>
       </c>
@@ -17445,7 +17441,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>1193</v>
       </c>
@@ -17471,7 +17467,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>1197</v>
       </c>
@@ -17497,7 +17493,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1201</v>
       </c>
@@ -17523,7 +17519,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1205</v>
       </c>
@@ -17549,7 +17545,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>1209</v>
       </c>
@@ -17575,7 +17571,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>1213</v>
       </c>
@@ -17601,7 +17597,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>1217</v>
       </c>
@@ -17627,7 +17623,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>1221</v>
       </c>
@@ -17653,7 +17649,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>1225</v>
       </c>
@@ -17679,7 +17675,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>1229</v>
       </c>
@@ -17708,7 +17704,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>1233</v>
       </c>
@@ -17737,7 +17733,7 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>1237</v>
       </c>
@@ -17763,7 +17759,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>1241</v>
       </c>
@@ -17789,7 +17785,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>1245</v>
       </c>
@@ -17815,7 +17811,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>1249</v>
       </c>
@@ -17841,7 +17837,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>161</v>
       </c>
@@ -17867,7 +17863,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>1255</v>
       </c>
@@ -17893,7 +17889,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>1259</v>
       </c>
@@ -17919,7 +17915,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>1263</v>
       </c>
@@ -17948,7 +17944,7 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>1267</v>
       </c>
@@ -17977,7 +17973,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>122</v>
       </c>
@@ -18003,7 +17999,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>1272</v>
       </c>
@@ -18032,7 +18028,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>128</v>
       </c>
@@ -18058,7 +18054,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>134</v>
       </c>
@@ -18084,7 +18080,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>741</v>
       </c>
@@ -18113,7 +18109,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>647</v>
       </c>
@@ -18139,7 +18135,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>715</v>
       </c>
@@ -18165,7 +18161,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>798</v>
       </c>
@@ -18191,7 +18187,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>829</v>
       </c>
@@ -18217,7 +18213,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>1281</v>
       </c>
@@ -18243,7 +18239,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>1285</v>
       </c>
@@ -18269,7 +18265,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>1287</v>
       </c>
@@ -18295,7 +18291,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>1289</v>
       </c>
@@ -18324,7 +18320,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>1292</v>
       </c>
@@ -18353,7 +18349,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>1296</v>
       </c>
@@ -18382,7 +18378,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>1300</v>
       </c>
@@ -18411,7 +18407,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>1304</v>
       </c>
@@ -18444,7 +18440,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>170</v>
       </c>
@@ -18470,7 +18466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>1308</v>
       </c>
@@ -18500,7 +18496,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>210</v>
       </c>
@@ -18526,7 +18522,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>50</v>
       </c>
@@ -18555,7 +18551,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>54</v>
       </c>
@@ -18584,7 +18580,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>58</v>
       </c>
@@ -18613,7 +18609,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>1311</v>
       </c>
@@ -18642,7 +18638,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>1315</v>
       </c>
@@ -18671,7 +18667,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>1319</v>
       </c>
@@ -18700,7 +18696,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>1323</v>
       </c>
@@ -18729,7 +18725,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="411" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A411" s="5" t="s">
         <v>1327</v>
       </c>
@@ -18758,7 +18754,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="412" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
         <v>1331</v>
       </c>
@@ -18785,7 +18781,7 @@
       </c>
       <c r="I412" s="3"/>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>1336</v>
       </c>
@@ -18813,7 +18809,7 @@
       <c r="I413" s="5"/>
       <c r="J413" s="5"/>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>1340</v>
       </c>
@@ -18843,7 +18839,7 @@
       </c>
       <c r="J414" s="5"/>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>1344</v>
       </c>
@@ -18871,7 +18867,7 @@
       <c r="I415" s="5"/>
       <c r="J415" s="5"/>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>1348</v>
       </c>
@@ -18899,7 +18895,7 @@
       <c r="I416" s="5"/>
       <c r="J416" s="5"/>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>1352</v>
       </c>
@@ -18927,7 +18923,7 @@
       <c r="I417" s="5"/>
       <c r="J417" s="5"/>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>1356</v>
       </c>
@@ -18955,7 +18951,7 @@
       <c r="I418" s="5"/>
       <c r="J418" s="5"/>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>1360</v>
       </c>
@@ -18985,7 +18981,7 @@
       </c>
       <c r="J419" s="5"/>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>1364</v>
       </c>
@@ -19013,7 +19009,7 @@
       <c r="I420" s="5"/>
       <c r="J420" s="5"/>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>1065</v>
       </c>
@@ -19043,7 +19039,7 @@
       </c>
       <c r="J421" s="5"/>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1371</v>
       </c>
@@ -19071,7 +19067,7 @@
       <c r="I422" s="5"/>
       <c r="J422" s="5"/>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1373</v>
       </c>
@@ -19099,7 +19095,7 @@
       <c r="I423" s="5"/>
       <c r="J423" s="5"/>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>1377</v>
       </c>
@@ -19127,7 +19123,7 @@
       <c r="I424" s="5"/>
       <c r="J424" s="5"/>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1381</v>
       </c>
@@ -19157,7 +19153,7 @@
       </c>
       <c r="J425" s="5"/>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1385</v>
       </c>
@@ -19185,7 +19181,7 @@
       <c r="I426" s="5"/>
       <c r="J426" s="5"/>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1389</v>
       </c>
@@ -19215,7 +19211,7 @@
       </c>
       <c r="J427" s="5"/>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1105</v>
       </c>
@@ -19245,7 +19241,7 @@
       </c>
       <c r="J428" s="5"/>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1395</v>
       </c>
@@ -19273,7 +19269,7 @@
       <c r="I429" s="5"/>
       <c r="J429" s="5"/>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1399</v>
       </c>
@@ -19301,7 +19297,7 @@
       <c r="I430" s="5"/>
       <c r="J430" s="5"/>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1403</v>
       </c>
@@ -19329,7 +19325,7 @@
       <c r="I431" s="5"/>
       <c r="J431" s="5"/>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1407</v>
       </c>
@@ -19357,7 +19353,7 @@
       <c r="I432" s="5"/>
       <c r="J432" s="5"/>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>167</v>
       </c>
@@ -19385,7 +19381,7 @@
       <c r="I433" s="5"/>
       <c r="J433" s="5"/>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1413</v>
       </c>
@@ -19413,7 +19409,7 @@
       <c r="I434" s="5"/>
       <c r="J434" s="5"/>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1417</v>
       </c>
@@ -19441,7 +19437,7 @@
       <c r="I435" s="5"/>
       <c r="J435" s="5"/>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1081</v>
       </c>
@@ -19469,7 +19465,7 @@
       <c r="I436" s="5"/>
       <c r="J436" s="5"/>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1424</v>
       </c>
@@ -19499,7 +19495,7 @@
       </c>
       <c r="J437" s="5"/>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>1428</v>
       </c>
@@ -19527,7 +19523,7 @@
       <c r="I438" s="5"/>
       <c r="J438" s="5"/>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>1432</v>
       </c>
@@ -19557,7 +19553,7 @@
       </c>
       <c r="J439" s="5"/>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>1436</v>
       </c>
@@ -19587,7 +19583,7 @@
       </c>
       <c r="J440" s="5"/>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>1440</v>
       </c>
@@ -19615,7 +19611,7 @@
       <c r="I441" s="5"/>
       <c r="J441" s="5"/>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>1444</v>
       </c>
@@ -19643,7 +19639,7 @@
       <c r="I442" s="5"/>
       <c r="J442" s="5"/>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1448</v>
       </c>
@@ -19671,7 +19667,7 @@
       <c r="I443" s="5"/>
       <c r="J443" s="5"/>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1452</v>
       </c>
@@ -19699,7 +19695,7 @@
       <c r="I444" s="5"/>
       <c r="J444" s="5"/>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1456</v>
       </c>
@@ -19727,7 +19723,7 @@
       <c r="I445" s="5"/>
       <c r="J445" s="5"/>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1460</v>
       </c>
@@ -19755,7 +19751,7 @@
       <c r="I446" s="5"/>
       <c r="J446" s="5"/>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1464</v>
       </c>
@@ -19783,7 +19779,7 @@
       <c r="I447" s="5"/>
       <c r="J447" s="5"/>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1468</v>
       </c>
@@ -19811,7 +19807,7 @@
       <c r="I448" s="5"/>
       <c r="J448" s="5"/>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1472</v>
       </c>
@@ -19839,7 +19835,7 @@
       <c r="I449" s="5"/>
       <c r="J449" s="5"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1476</v>
       </c>
@@ -19867,7 +19863,7 @@
       <c r="I450" s="5"/>
       <c r="J450" s="5"/>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1480</v>
       </c>
@@ -19895,7 +19891,7 @@
       <c r="I451" s="5"/>
       <c r="J451" s="5"/>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1484</v>
       </c>
@@ -19923,7 +19919,7 @@
       <c r="I452" s="5"/>
       <c r="J452" s="5"/>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1488</v>
       </c>
@@ -19951,7 +19947,7 @@
       <c r="I453" s="5"/>
       <c r="J453" s="5"/>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>1492</v>
       </c>
@@ -19979,7 +19975,7 @@
       <c r="I454" s="5"/>
       <c r="J454" s="5"/>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>1496</v>
       </c>
@@ -20007,7 +20003,7 @@
       <c r="I455" s="5"/>
       <c r="J455" s="5"/>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1500</v>
       </c>
@@ -20035,7 +20031,7 @@
       <c r="I456" s="5"/>
       <c r="J456" s="5"/>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1504</v>
       </c>
@@ -20063,7 +20059,7 @@
       <c r="I457" s="5"/>
       <c r="J457" s="5"/>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>1508</v>
       </c>
@@ -20091,7 +20087,7 @@
       <c r="I458" s="5"/>
       <c r="J458" s="5"/>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1511</v>
       </c>
@@ -20121,7 +20117,7 @@
       </c>
       <c r="J459" s="5"/>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1515</v>
       </c>
@@ -20149,7 +20145,7 @@
       <c r="I460" s="5"/>
       <c r="J460" s="5"/>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1519</v>
       </c>
@@ -20177,7 +20173,7 @@
       <c r="I461" s="5"/>
       <c r="J461" s="5"/>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1523</v>
       </c>
@@ -20205,7 +20201,7 @@
       <c r="I462" s="5"/>
       <c r="J462" s="5"/>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>134</v>
       </c>
@@ -20233,7 +20229,7 @@
       <c r="I463" s="5"/>
       <c r="J463" s="5"/>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>741</v>
       </c>
@@ -20263,7 +20259,7 @@
       </c>
       <c r="J464" s="5"/>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>647</v>
       </c>
@@ -20291,7 +20287,7 @@
       <c r="I465" s="5"/>
       <c r="J465" s="5"/>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>715</v>
       </c>
@@ -20319,7 +20315,7 @@
       <c r="I466" s="5"/>
       <c r="J466" s="5"/>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>798</v>
       </c>
@@ -20347,7 +20343,7 @@
       <c r="I467" s="5"/>
       <c r="J467" s="5"/>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>829</v>
       </c>
@@ -20375,7 +20371,7 @@
       <c r="I468" s="5"/>
       <c r="J468" s="5"/>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>1281</v>
       </c>
@@ -20405,7 +20401,7 @@
       </c>
       <c r="J469" s="5"/>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>1285</v>
       </c>
@@ -20433,7 +20429,7 @@
       <c r="I470" s="5"/>
       <c r="J470" s="5"/>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>1287</v>
       </c>
@@ -20461,7 +20457,7 @@
       <c r="I471" s="5"/>
       <c r="J471" s="5"/>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>1289</v>
       </c>
@@ -20491,7 +20487,7 @@
       </c>
       <c r="J472" s="5"/>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>1292</v>
       </c>
@@ -20521,7 +20517,7 @@
       </c>
       <c r="J473" s="5"/>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>1296</v>
       </c>
@@ -20551,7 +20547,7 @@
       </c>
       <c r="J474" s="5"/>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>5</v>
       </c>
@@ -20581,7 +20577,7 @@
       </c>
       <c r="J475" s="5"/>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>10</v>
       </c>
@@ -20611,7 +20607,7 @@
       </c>
       <c r="J476" s="5"/>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>14</v>
       </c>
@@ -20641,7 +20637,7 @@
       </c>
       <c r="J477" s="5"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>18</v>
       </c>
@@ -20671,7 +20667,7 @@
       </c>
       <c r="J478" s="5"/>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>22</v>
       </c>
@@ -20701,7 +20697,7 @@
       </c>
       <c r="J479" s="5"/>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>26</v>
       </c>
@@ -20731,7 +20727,7 @@
       </c>
       <c r="J480" s="5"/>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>30</v>
       </c>
@@ -20761,7 +20757,7 @@
       </c>
       <c r="J481" s="5"/>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>34</v>
       </c>
@@ -20791,7 +20787,7 @@
       </c>
       <c r="J482" s="5"/>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>38</v>
       </c>
@@ -20821,7 +20817,7 @@
       </c>
       <c r="J483" s="5"/>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>42</v>
       </c>
@@ -20851,7 +20847,7 @@
       </c>
       <c r="J484" s="5"/>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>46</v>
       </c>
@@ -20881,7 +20877,7 @@
       </c>
       <c r="J485" s="5"/>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>175</v>
       </c>
@@ -20911,7 +20907,7 @@
       </c>
       <c r="J486" s="5"/>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>54</v>
       </c>
@@ -20941,7 +20937,7 @@
       </c>
       <c r="J487" s="5"/>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>58</v>
       </c>
@@ -20971,7 +20967,7 @@
       </c>
       <c r="J488" s="5"/>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>1311</v>
       </c>
@@ -21001,7 +20997,7 @@
       </c>
       <c r="J489" s="5"/>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>1315</v>
       </c>
@@ -21031,7 +21027,7 @@
       </c>
       <c r="J490" s="5"/>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>1319</v>
       </c>
@@ -21061,7 +21057,7 @@
       </c>
       <c r="J491" s="5"/>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>1323</v>
       </c>
@@ -21091,7 +21087,7 @@
       </c>
       <c r="J492" s="5"/>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>1327</v>
       </c>
@@ -21121,7 +21117,7 @@
       </c>
       <c r="J493" s="5"/>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>1527</v>
       </c>
@@ -21151,7 +21147,7 @@
       </c>
       <c r="J494" s="5"/>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>1531</v>
       </c>
@@ -21181,7 +21177,7 @@
       </c>
       <c r="J495" s="5"/>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A496" s="3" t="s">
         <v>523</v>
       </c>
@@ -21208,7 +21204,7 @@
       </c>
       <c r="I496" s="3"/>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>611</v>
       </c>
@@ -21234,7 +21230,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>723</v>
       </c>
@@ -21263,7 +21259,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>1545</v>
       </c>
@@ -21289,7 +21285,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>1549</v>
       </c>
@@ -21315,7 +21311,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>1553</v>
       </c>
@@ -21341,7 +21337,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>1557</v>
       </c>
@@ -21367,7 +21363,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>1561</v>
       </c>
@@ -21396,7 +21392,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>1043</v>
       </c>
@@ -21422,7 +21418,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>1568</v>
       </c>
@@ -21448,7 +21444,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>1572</v>
       </c>
@@ -21474,7 +21470,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>1576</v>
       </c>
@@ -21500,7 +21496,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>1580</v>
       </c>
@@ -21526,7 +21522,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>1582</v>
       </c>
@@ -21552,7 +21548,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>1586</v>
       </c>
@@ -21578,7 +21574,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>1590</v>
       </c>
@@ -21604,7 +21600,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>1592</v>
       </c>
@@ -21630,7 +21626,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>1596</v>
       </c>
@@ -21656,7 +21652,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>1598</v>
       </c>
@@ -21682,7 +21678,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>1602</v>
       </c>
@@ -21708,7 +21704,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>1606</v>
       </c>
@@ -21734,7 +21730,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>1610</v>
       </c>
@@ -21760,7 +21756,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>1614</v>
       </c>
@@ -21786,7 +21782,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>1618</v>
       </c>
@@ -21812,7 +21808,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>1622</v>
       </c>
@@ -21838,7 +21834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>1626</v>
       </c>
@@ -21867,7 +21863,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>1630</v>
       </c>
@@ -21893,7 +21889,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>1634</v>
       </c>
@@ -21919,7 +21915,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>1638</v>
       </c>
@@ -21945,7 +21941,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>1642</v>
       </c>
@@ -21971,7 +21967,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>1646</v>
       </c>
@@ -22000,7 +21996,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>1650</v>
       </c>
@@ -22026,7 +22022,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>1654</v>
       </c>
@@ -22055,7 +22051,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>1658</v>
       </c>
@@ -22084,7 +22080,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>1662</v>
       </c>
@@ -22110,7 +22106,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>1666</v>
       </c>
@@ -22139,7 +22135,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>1670</v>
       </c>
@@ -22165,7 +22161,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>1674</v>
       </c>
@@ -22191,7 +22187,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>1678</v>
       </c>
@@ -22217,7 +22213,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>1682</v>
       </c>
@@ -22243,7 +22239,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>1684</v>
       </c>
@@ -22269,7 +22265,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>1688</v>
       </c>
@@ -22295,7 +22291,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>1692</v>
       </c>
@@ -22324,7 +22320,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>1696</v>
       </c>
@@ -22350,7 +22346,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>1700</v>
       </c>
@@ -22376,7 +22372,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>1704</v>
       </c>
@@ -22402,7 +22398,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>1708</v>
       </c>
@@ -22428,7 +22424,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>1712</v>
       </c>
@@ -22454,7 +22450,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>1716</v>
       </c>
@@ -22480,7 +22476,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>1720</v>
       </c>
@@ -22506,7 +22502,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>1724</v>
       </c>
@@ -22535,7 +22531,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>1726</v>
       </c>
@@ -22561,7 +22557,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>1730</v>
       </c>
@@ -22590,7 +22586,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>1734</v>
       </c>
@@ -22619,7 +22615,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>1738</v>
       </c>
@@ -22648,7 +22644,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>1742</v>
       </c>
@@ -22674,7 +22670,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>1746</v>
       </c>
@@ -22700,7 +22696,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>1750</v>
       </c>
@@ -22726,7 +22722,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>1754</v>
       </c>
@@ -22755,7 +22751,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>1308</v>
       </c>
@@ -22781,7 +22777,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>1761</v>
       </c>
@@ -22807,7 +22803,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>1765</v>
       </c>
@@ -22833,7 +22829,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>1769</v>
       </c>
@@ -22859,7 +22855,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>1773</v>
       </c>
@@ -22885,7 +22881,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>1777</v>
       </c>
@@ -22911,7 +22907,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>1781</v>
       </c>
@@ -22937,7 +22933,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>1785</v>
       </c>
@@ -22963,7 +22959,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>1789</v>
       </c>
@@ -22989,7 +22985,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>1793</v>
       </c>
@@ -23015,7 +23011,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>5</v>
       </c>
@@ -23044,7 +23040,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>10</v>
       </c>
@@ -23073,7 +23069,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>14</v>
       </c>
@@ -23102,7 +23098,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>18</v>
       </c>
@@ -23131,7 +23127,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>22</v>
       </c>
@@ -23160,7 +23156,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>26</v>
       </c>
@@ -23189,7 +23185,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>30</v>
       </c>
@@ -23218,7 +23214,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>34</v>
       </c>
@@ -23247,7 +23243,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>38</v>
       </c>
@@ -23276,7 +23272,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>42</v>
       </c>
@@ -23305,7 +23301,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>46</v>
       </c>
@@ -23334,7 +23330,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>175</v>
       </c>
@@ -23363,7 +23359,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>54</v>
       </c>
@@ -23392,7 +23388,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>58</v>
       </c>
@@ -23421,7 +23417,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>1311</v>
       </c>
@@ -23450,7 +23446,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>1315</v>
       </c>
@@ -23479,7 +23475,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>1319</v>
       </c>
@@ -23508,7 +23504,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>1323</v>
       </c>
@@ -23537,7 +23533,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>1327</v>
       </c>
@@ -23566,7 +23562,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>1527</v>
       </c>
@@ -23595,7 +23591,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>1531</v>
       </c>
@@ -23624,7 +23620,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A586" s="6" t="s">
         <v>1830</v>
       </c>
@@ -23653,7 +23649,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A587" s="17" t="s">
         <v>1930</v>
       </c>
@@ -23682,7 +23678,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A588" s="17" t="s">
         <v>1931</v>
       </c>
@@ -23711,7 +23707,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A589" s="17" t="s">
         <v>1840</v>
       </c>
@@ -23740,7 +23736,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A590" s="17" t="s">
         <v>1932</v>
       </c>
@@ -23769,7 +23765,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A591" s="17" t="s">
         <v>1804</v>
       </c>
@@ -23798,7 +23794,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A592" s="17" t="s">
         <v>1819</v>
       </c>
@@ -23827,7 +23823,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A593" s="17" t="s">
         <v>1939</v>
       </c>
@@ -23856,7 +23852,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A594" s="17" t="s">
         <v>1798</v>
       </c>
@@ -23885,7 +23881,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A595" s="17" t="s">
         <v>1940</v>
       </c>
@@ -23914,7 +23910,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A596" s="20" t="s">
         <v>1941</v>
       </c>
@@ -23943,7 +23939,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A597" s="17" t="s">
         <v>1933</v>
       </c>
@@ -23972,7 +23968,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A598" s="17" t="s">
         <v>1934</v>
       </c>
@@ -24001,7 +23997,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A599" s="17" t="s">
         <v>1935</v>
       </c>
@@ -24030,7 +24026,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A600" s="17" t="s">
         <v>1936</v>
       </c>
@@ -24059,7 +24055,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A601" s="17" t="s">
         <v>1937</v>
       </c>
@@ -24088,7 +24084,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A602" s="17" t="s">
         <v>1938</v>
       </c>
@@ -24117,7 +24113,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A603" s="17" t="s">
         <v>1801</v>
       </c>
@@ -24146,7 +24142,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A604" s="17" t="s">
         <v>1942</v>
       </c>
@@ -24175,7 +24171,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A605" s="17" t="s">
         <v>1943</v>
       </c>
@@ -24204,7 +24200,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A606" s="17" t="s">
         <v>1944</v>
       </c>
@@ -24233,7 +24229,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A607" s="17" t="s">
         <v>1945</v>
       </c>
@@ -24262,7 +24258,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A608" s="17" t="s">
         <v>798</v>
       </c>
@@ -24291,7 +24287,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A609" s="17" t="s">
         <v>1946</v>
       </c>
@@ -24320,7 +24316,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A610" s="17" t="s">
         <v>1947</v>
       </c>
@@ -24349,7 +24345,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A611" s="17" t="s">
         <v>1948</v>
       </c>
@@ -24378,7 +24374,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A612" s="17" t="s">
         <v>1949</v>
       </c>
@@ -24407,7 +24403,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A613" s="17" t="s">
         <v>1833</v>
       </c>
@@ -24436,7 +24432,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A614" s="17" t="s">
         <v>1848</v>
       </c>
@@ -24465,7 +24461,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A615" s="17" t="s">
         <v>1839</v>
       </c>
@@ -24494,7 +24490,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A616" s="17" t="s">
         <v>1953</v>
       </c>
@@ -24523,7 +24519,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A617" s="17" t="s">
         <v>1954</v>
       </c>
@@ -24552,7 +24548,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A618" s="17" t="s">
         <v>1955</v>
       </c>
@@ -24581,7 +24577,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A619" s="17" t="s">
         <v>1956</v>
       </c>
@@ -24610,7 +24606,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A620" s="17" t="s">
         <v>1957</v>
       </c>
@@ -24639,7 +24635,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A621" s="17" t="s">
         <v>1958</v>
       </c>
@@ -24668,7 +24664,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A622" s="17" t="s">
         <v>1832</v>
       </c>
@@ -24697,7 +24693,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A623" s="17" t="s">
         <v>1950</v>
       </c>
@@ -24726,7 +24722,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A624" s="17" t="s">
         <v>1951</v>
       </c>
@@ -24755,7 +24751,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A625" s="17" t="s">
         <v>1952</v>
       </c>
@@ -24784,7 +24780,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A626" s="17" t="s">
         <v>739</v>
       </c>
@@ -24813,7 +24809,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A627" s="17" t="s">
         <v>1821</v>
       </c>
@@ -24842,7 +24838,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A628" s="17" t="s">
         <v>1841</v>
       </c>
@@ -24871,7 +24867,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A629" s="17" t="s">
         <v>1824</v>
       </c>
@@ -24900,7 +24896,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A630" s="17" t="s">
         <v>1827</v>
       </c>
@@ -24929,7 +24925,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A631" s="17" t="s">
         <v>1959</v>
       </c>
@@ -24958,7 +24954,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A632" s="17" t="s">
         <v>1960</v>
       </c>
@@ -24987,7 +24983,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A633" s="17" t="s">
         <v>1287</v>
       </c>
@@ -25016,7 +25012,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A634" s="17" t="s">
         <v>1837</v>
       </c>
@@ -25045,7 +25041,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A635" s="17" t="s">
         <v>1812</v>
       </c>
@@ -25074,7 +25070,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A636" s="17" t="s">
         <v>1845</v>
       </c>
@@ -25103,7 +25099,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A637" s="17" t="s">
         <v>1797</v>
       </c>
@@ -25132,7 +25128,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A638" s="17" t="s">
         <v>1961</v>
       </c>
@@ -25161,7 +25157,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A639" s="17" t="s">
         <v>1971</v>
       </c>
@@ -25184,7 +25180,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A640" s="17" t="s">
         <v>1970</v>
       </c>
@@ -25207,7 +25203,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A641" s="17" t="s">
         <v>1966</v>
       </c>
@@ -25230,7 +25226,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A642" s="17" t="s">
         <v>1969</v>
       </c>
@@ -25253,7 +25249,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A643" s="17" t="s">
         <v>1974</v>
       </c>
@@ -25276,7 +25272,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A644" s="17" t="s">
         <v>1978</v>
       </c>
@@ -25299,7 +25295,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A645" s="17" t="s">
         <v>1981</v>
       </c>

--- a/metadata/C3H10_10X_Metadata.xlsx
+++ b/metadata/C3H10_10X_Metadata.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\updeplanas2.epfl.ch\DeplanckeNAS2\TF-seq\Wangjie\TF-seq_GitHub\TF-seq\metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\projects\TF-seq\Wangjie\TF-seq_GitHub\TF-seq\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D53707-E8BC-4CB8-8AAB-43DF80E2A947}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6356857-F308-4140-BB3F-CB906F2E8688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1305" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C3H10_10X_Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4089" uniqueCount="1991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4185" uniqueCount="2004">
   <si>
     <t>TF_name</t>
   </si>
@@ -6747,6 +6758,45 @@
   </si>
   <si>
     <t>Renamed Tada2a</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>exp14</t>
+  </si>
+  <si>
+    <t>Plate0-B1</t>
+  </si>
+  <si>
+    <t>Plate0-C9</t>
+  </si>
+  <si>
+    <t>Plate1-E12</t>
+  </si>
+  <si>
+    <t>Plate1-F10</t>
+  </si>
+  <si>
+    <t>Plate1-F6</t>
+  </si>
+  <si>
+    <t>Plate1-F8</t>
+  </si>
+  <si>
+    <t>Plate6-B7</t>
+  </si>
+  <si>
+    <t>Plate6-E12</t>
+  </si>
+  <si>
+    <t>Zfp24</t>
+  </si>
+  <si>
+    <t>Plate6-C10</t>
+  </si>
+  <si>
+    <t>Plate6-F12</t>
   </si>
 </sst>
 </file>
@@ -7247,7 +7297,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="7"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
@@ -7269,6 +7319,19 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="35" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="35" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -7625,26 +7688,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L645"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J661"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="15" t="s">
@@ -7669,11 +7732,11 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -7698,11 +7761,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
@@ -7727,11 +7790,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="23" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
@@ -7756,11 +7819,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
@@ -7785,11 +7848,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
@@ -7814,11 +7877,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
@@ -7843,11 +7906,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="23" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
@@ -7872,11 +7935,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>34</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="23" t="s">
         <v>35</v>
       </c>
       <c r="C9" t="s">
@@ -7901,11 +7964,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C10" t="s">
@@ -7929,20 +7992,12 @@
       <c r="I10" s="11" t="s">
         <v>1987</v>
       </c>
-      <c r="K10">
-        <f>SUM(G9:G12)</f>
-        <v>261</v>
-      </c>
-      <c r="L10">
-        <f>SUM(H9:H12)</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>42</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C11" t="s">
@@ -7967,11 +8022,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>46</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="23" t="s">
         <v>47</v>
       </c>
       <c r="C12" t="s">
@@ -7996,11 +8051,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="23" t="s">
         <v>51</v>
       </c>
       <c r="C13" t="s">
@@ -8025,11 +8080,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="23" t="s">
         <v>55</v>
       </c>
       <c r="C14" t="s">
@@ -8054,11 +8109,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>58</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="23" t="s">
         <v>59</v>
       </c>
       <c r="C15" t="s">
@@ -8083,11 +8138,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>62</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="23">
         <v>1</v>
       </c>
       <c r="C16" t="s">
@@ -8109,11 +8164,11 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>65</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="23">
         <v>2</v>
       </c>
       <c r="C17" t="s">
@@ -8135,11 +8190,11 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="23">
         <v>5</v>
       </c>
       <c r="C18" t="s">
@@ -8161,11 +8216,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>71</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="23">
         <v>6</v>
       </c>
       <c r="C19" t="s">
@@ -8187,11 +8242,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>74</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="23">
         <v>7</v>
       </c>
       <c r="C20" t="s">
@@ -8213,11 +8268,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>77</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="23">
         <v>8</v>
       </c>
       <c r="C21" t="s">
@@ -8239,11 +8294,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>80</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="23">
         <v>12</v>
       </c>
       <c r="C22" t="s">
@@ -8265,11 +8320,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>83</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="23">
         <v>13</v>
       </c>
       <c r="C23" t="s">
@@ -8291,11 +8346,11 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>86</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="23">
         <v>14</v>
       </c>
       <c r="C24" t="s">
@@ -8317,11 +8372,11 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>89</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="23">
         <v>15</v>
       </c>
       <c r="C25" t="s">
@@ -8343,11 +8398,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>92</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="23">
         <v>16</v>
       </c>
       <c r="C26" t="s">
@@ -8369,11 +8424,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>95</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="23">
         <v>17</v>
       </c>
       <c r="C27" t="s">
@@ -8395,11 +8450,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>98</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="23">
         <v>18</v>
       </c>
       <c r="C28" t="s">
@@ -8421,11 +8476,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>101</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="23">
         <v>19</v>
       </c>
       <c r="C29" t="s">
@@ -8447,11 +8502,11 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>104</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="23">
         <v>20</v>
       </c>
       <c r="C30" t="s">
@@ -8473,11 +8528,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>107</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="23">
         <v>21</v>
       </c>
       <c r="C31" t="s">
@@ -8499,11 +8554,11 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>110</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="23">
         <v>22</v>
       </c>
       <c r="C32" t="s">
@@ -8525,11 +8580,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>113</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="23">
         <v>23</v>
       </c>
       <c r="C33" t="s">
@@ -8551,11 +8606,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>116</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="23">
         <v>24</v>
       </c>
       <c r="C34" t="s">
@@ -8577,11 +8632,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="23">
         <v>25</v>
       </c>
       <c r="C35" t="s">
@@ -8603,11 +8658,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>122</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="23">
         <v>26</v>
       </c>
       <c r="C36" t="s">
@@ -8629,11 +8684,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>125</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="23">
         <v>27</v>
       </c>
       <c r="C37" t="s">
@@ -8655,11 +8710,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>128</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="23">
         <v>30</v>
       </c>
       <c r="C38" t="s">
@@ -8681,11 +8736,11 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>131</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="23">
         <v>31</v>
       </c>
       <c r="C39" t="s">
@@ -8707,11 +8762,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>134</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="23">
         <v>33</v>
       </c>
       <c r="C40" t="s">
@@ -8733,11 +8788,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>137</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="23">
         <v>34</v>
       </c>
       <c r="C41" t="s">
@@ -8759,11 +8814,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>140</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="23">
         <v>35</v>
       </c>
       <c r="C42" t="s">
@@ -8785,11 +8840,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>143</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="23">
         <v>36</v>
       </c>
       <c r="C43" t="s">
@@ -8814,11 +8869,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>146</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="23">
         <v>38</v>
       </c>
       <c r="C44" t="s">
@@ -8840,11 +8895,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>149</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="23">
         <v>39</v>
       </c>
       <c r="C45" t="s">
@@ -8866,11 +8921,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>152</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="23">
         <v>41</v>
       </c>
       <c r="C46" t="s">
@@ -8892,11 +8947,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>155</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="23">
         <v>42</v>
       </c>
       <c r="C47" t="s">
@@ -8918,11 +8973,11 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>158</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="23">
         <v>44</v>
       </c>
       <c r="C48" t="s">
@@ -8944,11 +8999,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>161</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="23">
         <v>45</v>
       </c>
       <c r="C49" t="s">
@@ -8970,11 +9025,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>164</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="23">
         <v>50</v>
       </c>
       <c r="C50" t="s">
@@ -8996,11 +9051,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>167</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="23">
         <v>52</v>
       </c>
       <c r="C51" t="s">
@@ -9022,11 +9077,11 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>170</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="23" t="s">
         <v>171</v>
       </c>
       <c r="C52" t="s">
@@ -9048,11 +9103,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="3" t="s">
@@ -9077,11 +9132,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -9106,11 +9161,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>14</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="23" t="s">
         <v>15</v>
       </c>
       <c r="C55" t="s">
@@ -9135,11 +9190,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>18</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C56" t="s">
@@ -9164,11 +9219,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>22</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C57" t="s">
@@ -9193,11 +9248,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>26</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C58" t="s">
@@ -9222,11 +9277,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>30</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="23" t="s">
         <v>31</v>
       </c>
       <c r="C59" t="s">
@@ -9251,11 +9306,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>34</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="23" t="s">
         <v>35</v>
       </c>
       <c r="C60" t="s">
@@ -9280,11 +9335,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>38</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C61" t="s">
@@ -9309,11 +9364,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>42</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C62" t="s">
@@ -9338,11 +9393,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>46</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="23" t="s">
         <v>47</v>
       </c>
       <c r="C63" t="s">
@@ -9367,11 +9422,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>175</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="23" t="s">
         <v>176</v>
       </c>
       <c r="C64" t="s">
@@ -9396,11 +9451,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>50</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="23" t="s">
         <v>51</v>
       </c>
       <c r="C65" t="s">
@@ -9425,11 +9480,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>54</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="23" t="s">
         <v>55</v>
       </c>
       <c r="C66" t="s">
@@ -9454,11 +9509,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>58</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="23" t="s">
         <v>59</v>
       </c>
       <c r="C67" t="s">
@@ -9483,11 +9538,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>179</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="23" t="s">
         <v>180</v>
       </c>
       <c r="C68" t="s">
@@ -9509,11 +9564,11 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>183</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="23" t="s">
         <v>184</v>
       </c>
       <c r="C69" t="s">
@@ -9538,11 +9593,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>89</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="23" t="s">
         <v>187</v>
       </c>
       <c r="C70" t="s">
@@ -9564,11 +9619,11 @@
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>190</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="23" t="s">
         <v>191</v>
       </c>
       <c r="C71" t="s">
@@ -9590,11 +9645,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>194</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="23" t="s">
         <v>195</v>
       </c>
       <c r="C72" t="s">
@@ -9616,11 +9671,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>198</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="23" t="s">
         <v>199</v>
       </c>
       <c r="C73" t="s">
@@ -9642,11 +9697,11 @@
         <v>44</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>202</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="23" t="s">
         <v>203</v>
       </c>
       <c r="C74" t="s">
@@ -9668,11 +9723,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>206</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="23" t="s">
         <v>207</v>
       </c>
       <c r="C75" t="s">
@@ -9697,11 +9752,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>210</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="23" t="s">
         <v>211</v>
       </c>
       <c r="C76" t="s">
@@ -9723,11 +9778,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>214</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="23" t="s">
         <v>215</v>
       </c>
       <c r="C77" t="s">
@@ -9749,11 +9804,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>218</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="23" t="s">
         <v>219</v>
       </c>
       <c r="C78" t="s">
@@ -9775,11 +9830,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>222</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="23" t="s">
         <v>223</v>
       </c>
       <c r="C79" t="s">
@@ -9804,11 +9859,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>226</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="23" t="s">
         <v>227</v>
       </c>
       <c r="C80" t="s">
@@ -9833,11 +9888,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>230</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="23" t="s">
         <v>231</v>
       </c>
       <c r="C81" t="s">
@@ -9862,11 +9917,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>234</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="23" t="s">
         <v>235</v>
       </c>
       <c r="C82" t="s">
@@ -9888,11 +9943,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>238</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="23" t="s">
         <v>239</v>
       </c>
       <c r="C83" t="s">
@@ -9914,11 +9969,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>242</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="23" t="s">
         <v>243</v>
       </c>
       <c r="C84" t="s">
@@ -9940,11 +9995,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>246</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="23" t="s">
         <v>247</v>
       </c>
       <c r="C85" t="s">
@@ -9966,11 +10021,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>250</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="23" t="s">
         <v>251</v>
       </c>
       <c r="C86" t="s">
@@ -9992,11 +10047,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>254</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="23" t="s">
         <v>255</v>
       </c>
       <c r="C87" t="s">
@@ -10018,11 +10073,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>258</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="23" t="s">
         <v>259</v>
       </c>
       <c r="C88" t="s">
@@ -10047,11 +10102,11 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>262</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="23" t="s">
         <v>263</v>
       </c>
       <c r="C89" t="s">
@@ -10076,11 +10131,11 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>266</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="23" t="s">
         <v>267</v>
       </c>
       <c r="C90" t="s">
@@ -10105,11 +10160,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>270</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="23" t="s">
         <v>271</v>
       </c>
       <c r="C91" t="s">
@@ -10131,11 +10186,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>274</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="23" t="s">
         <v>275</v>
       </c>
       <c r="C92" t="s">
@@ -10160,11 +10215,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>278</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="23" t="s">
         <v>279</v>
       </c>
       <c r="C93" t="s">
@@ -10186,11 +10241,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>282</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="23" t="s">
         <v>283</v>
       </c>
       <c r="C94" t="s">
@@ -10215,11 +10270,11 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>286</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="23" t="s">
         <v>287</v>
       </c>
       <c r="C95" t="s">
@@ -10244,11 +10299,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>290</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="23" t="s">
         <v>291</v>
       </c>
       <c r="C96" t="s">
@@ -10270,11 +10325,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>294</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="23" t="s">
         <v>295</v>
       </c>
       <c r="C97" t="s">
@@ -10296,11 +10351,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>298</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="23" t="s">
         <v>299</v>
       </c>
       <c r="C98" t="s">
@@ -10325,11 +10380,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>302</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="23" t="s">
         <v>303</v>
       </c>
       <c r="C99" t="s">
@@ -10354,11 +10409,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>306</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="23" t="s">
         <v>307</v>
       </c>
       <c r="C100" t="s">
@@ -10383,11 +10438,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>310</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="23" t="s">
         <v>311</v>
       </c>
       <c r="C101" t="s">
@@ -10409,11 +10464,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>152</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="23" t="s">
         <v>314</v>
       </c>
       <c r="C102" t="s">
@@ -10438,11 +10493,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>317</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="23" t="s">
         <v>318</v>
       </c>
       <c r="C103" t="s">
@@ -10467,11 +10522,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>321</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="23" t="s">
         <v>322</v>
       </c>
       <c r="C104" t="s">
@@ -10493,11 +10548,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>325</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="23" t="s">
         <v>326</v>
       </c>
       <c r="C105" t="s">
@@ -10519,11 +10574,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>86</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="23" t="s">
         <v>329</v>
       </c>
       <c r="C106" t="s">
@@ -10548,11 +10603,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>77</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="23" t="s">
         <v>332</v>
       </c>
       <c r="C107" t="s">
@@ -10574,11 +10629,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>335</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="23" t="s">
         <v>336</v>
       </c>
       <c r="C108" t="s">
@@ -10603,11 +10658,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>339</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="23" t="s">
         <v>340</v>
       </c>
       <c r="C109" t="s">
@@ -10632,11 +10687,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>343</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="23" t="s">
         <v>344</v>
       </c>
       <c r="C110" t="s">
@@ -10661,11 +10716,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>347</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="23" t="s">
         <v>348</v>
       </c>
       <c r="C111" t="s">
@@ -10690,11 +10745,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>351</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="23" t="s">
         <v>352</v>
       </c>
       <c r="C112" t="s">
@@ -10716,11 +10771,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>355</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="23" t="s">
         <v>356</v>
       </c>
       <c r="C113" t="s">
@@ -10742,11 +10797,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>359</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="23" t="s">
         <v>360</v>
       </c>
       <c r="C114" t="s">
@@ -10768,11 +10823,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>363</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="23" t="s">
         <v>364</v>
       </c>
       <c r="C115" t="s">
@@ -10794,11 +10849,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>367</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="23" t="s">
         <v>368</v>
       </c>
       <c r="C116" t="s">
@@ -10823,11 +10878,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>371</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="23" t="s">
         <v>372</v>
       </c>
       <c r="C117" t="s">
@@ -10849,11 +10904,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>375</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="23" t="s">
         <v>376</v>
       </c>
       <c r="C118" t="s">
@@ -10878,11 +10933,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>379</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="23" t="s">
         <v>380</v>
       </c>
       <c r="C119" t="s">
@@ -10904,11 +10959,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>383</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="23" t="s">
         <v>384</v>
       </c>
       <c r="C120" t="s">
@@ -10933,11 +10988,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>387</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="23" t="s">
         <v>388</v>
       </c>
       <c r="C121" t="s">
@@ -10959,11 +11014,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>391</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="23" t="s">
         <v>392</v>
       </c>
       <c r="C122" t="s">
@@ -10988,11 +11043,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>395</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="23" t="s">
         <v>396</v>
       </c>
       <c r="C123" t="s">
@@ -11014,11 +11069,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>62</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="23" t="s">
         <v>399</v>
       </c>
       <c r="C124" t="s">
@@ -11043,11 +11098,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>402</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="23" t="s">
         <v>403</v>
       </c>
       <c r="C125" t="s">
@@ -11072,11 +11127,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>406</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="23" t="s">
         <v>407</v>
       </c>
       <c r="C126" t="s">
@@ -11098,11 +11153,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>410</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="23" t="s">
         <v>411</v>
       </c>
       <c r="C127" t="s">
@@ -11124,11 +11179,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>414</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="23" t="s">
         <v>415</v>
       </c>
       <c r="C128" t="s">
@@ -11150,11 +11205,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>418</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="23" t="s">
         <v>419</v>
       </c>
       <c r="C129" t="s">
@@ -11176,11 +11231,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>422</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="23" t="s">
         <v>423</v>
       </c>
       <c r="C130" t="s">
@@ -11202,11 +11257,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>426</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="23" t="s">
         <v>427</v>
       </c>
       <c r="C131" t="s">
@@ -11228,11 +11283,11 @@
         <v>62</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>430</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="23" t="s">
         <v>431</v>
       </c>
       <c r="C132" t="s">
@@ -11254,11 +11309,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>434</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="23" t="s">
         <v>435</v>
       </c>
       <c r="C133" t="s">
@@ -11280,11 +11335,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>438</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="23" t="s">
         <v>439</v>
       </c>
       <c r="C134" t="s">
@@ -11309,11 +11364,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>442</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="23" t="s">
         <v>443</v>
       </c>
       <c r="C135" t="s">
@@ -11335,11 +11390,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>446</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="23" t="s">
         <v>447</v>
       </c>
       <c r="C136" t="s">
@@ -11361,11 +11416,11 @@
         <v>37</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>450</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="23" t="s">
         <v>451</v>
       </c>
       <c r="C137" t="s">
@@ -11390,11 +11445,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>454</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="23" t="s">
         <v>455</v>
       </c>
       <c r="C138" t="s">
@@ -11416,11 +11471,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="22" t="s">
         <v>459</v>
       </c>
       <c r="C139" s="3" t="s">
@@ -11443,11 +11498,11 @@
       </c>
       <c r="I139" s="3"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>463</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="23" t="s">
         <v>464</v>
       </c>
       <c r="C140" t="s">
@@ -11469,11 +11524,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>467</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="23" t="s">
         <v>468</v>
       </c>
       <c r="C141" t="s">
@@ -11495,11 +11550,11 @@
         <v>102</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>471</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="23" t="s">
         <v>472</v>
       </c>
       <c r="C142" t="s">
@@ -11524,11 +11579,11 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>475</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="23" t="s">
         <v>476</v>
       </c>
       <c r="C143" t="s">
@@ -11553,11 +11608,11 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>479</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="23" t="s">
         <v>480</v>
       </c>
       <c r="C144" t="s">
@@ -11582,11 +11637,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>483</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="23" t="s">
         <v>484</v>
       </c>
       <c r="C145" t="s">
@@ -11608,11 +11663,11 @@
         <v>191</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>487</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="23" t="s">
         <v>488</v>
       </c>
       <c r="C146" t="s">
@@ -11634,11 +11689,11 @@
         <v>36</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>491</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="23" t="s">
         <v>492</v>
       </c>
       <c r="C147" t="s">
@@ -11660,11 +11715,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>495</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="23" t="s">
         <v>496</v>
       </c>
       <c r="C148" t="s">
@@ -11686,11 +11741,11 @@
         <v>87</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>499</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="23" t="s">
         <v>500</v>
       </c>
       <c r="C149" t="s">
@@ -11715,11 +11770,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>503</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="23" t="s">
         <v>504</v>
       </c>
       <c r="C150" t="s">
@@ -11741,11 +11796,11 @@
         <v>60</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>507</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="23" t="s">
         <v>508</v>
       </c>
       <c r="C151" t="s">
@@ -11767,11 +11822,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>511</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="23" t="s">
         <v>512</v>
       </c>
       <c r="C152" t="s">
@@ -11793,11 +11848,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>515</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="23" t="s">
         <v>516</v>
       </c>
       <c r="C153" t="s">
@@ -11819,11 +11874,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>519</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="23" t="s">
         <v>520</v>
       </c>
       <c r="C154" t="s">
@@ -11845,11 +11900,11 @@
         <v>60</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>523</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="23" t="s">
         <v>524</v>
       </c>
       <c r="C155" t="s">
@@ -11871,11 +11926,11 @@
         <v>189</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>527</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="23" t="s">
         <v>528</v>
       </c>
       <c r="C156" t="s">
@@ -11897,11 +11952,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>531</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="23" t="s">
         <v>532</v>
       </c>
       <c r="C157" t="s">
@@ -11923,11 +11978,11 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>535</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="23" t="s">
         <v>536</v>
       </c>
       <c r="C158" t="s">
@@ -11949,11 +12004,11 @@
         <v>99</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>539</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="23" t="s">
         <v>540</v>
       </c>
       <c r="C159" t="s">
@@ -11975,11 +12030,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>543</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="23" t="s">
         <v>544</v>
       </c>
       <c r="C160" t="s">
@@ -12001,11 +12056,11 @@
         <v>71</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>547</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="23" t="s">
         <v>548</v>
       </c>
       <c r="C161" t="s">
@@ -12030,11 +12085,11 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>551</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="23" t="s">
         <v>552</v>
       </c>
       <c r="C162" t="s">
@@ -12056,11 +12111,11 @@
         <v>87</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>555</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="23" t="s">
         <v>556</v>
       </c>
       <c r="C163" t="s">
@@ -12082,11 +12137,11 @@
         <v>102</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>559</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="23" t="s">
         <v>560</v>
       </c>
       <c r="C164" t="s">
@@ -12108,11 +12163,11 @@
         <v>97</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>563</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="23" t="s">
         <v>564</v>
       </c>
       <c r="C165" t="s">
@@ -12134,11 +12189,11 @@
         <v>128</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>567</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="23" t="s">
         <v>568</v>
       </c>
       <c r="C166" t="s">
@@ -12160,11 +12215,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>571</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="23" t="s">
         <v>572</v>
       </c>
       <c r="C167" t="s">
@@ -12186,11 +12241,11 @@
         <v>120</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>575</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="23" t="s">
         <v>576</v>
       </c>
       <c r="C168" t="s">
@@ -12212,11 +12267,11 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>579</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="23" t="s">
         <v>580</v>
       </c>
       <c r="C169" t="s">
@@ -12238,11 +12293,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>583</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="23" t="s">
         <v>584</v>
       </c>
       <c r="C170" t="s">
@@ -12264,11 +12319,11 @@
         <v>93</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>587</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="23" t="s">
         <v>588</v>
       </c>
       <c r="C171" t="s">
@@ -12290,11 +12345,11 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>591</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="23" t="s">
         <v>592</v>
       </c>
       <c r="C172" t="s">
@@ -12316,11 +12371,11 @@
         <v>141</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>595</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="23" t="s">
         <v>596</v>
       </c>
       <c r="C173" t="s">
@@ -12342,11 +12397,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>599</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="23" t="s">
         <v>600</v>
       </c>
       <c r="C174" t="s">
@@ -12368,11 +12423,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>603</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="23" t="s">
         <v>604</v>
       </c>
       <c r="C175" t="s">
@@ -12394,11 +12449,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>607</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="23" t="s">
         <v>608</v>
       </c>
       <c r="C176" t="s">
@@ -12420,11 +12475,11 @@
         <v>122</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>611</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="23" t="s">
         <v>612</v>
       </c>
       <c r="C177" t="s">
@@ -12446,11 +12501,11 @@
         <v>98</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>615</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="23" t="s">
         <v>616</v>
       </c>
       <c r="C178" t="s">
@@ -12472,11 +12527,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>619</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="23" t="s">
         <v>620</v>
       </c>
       <c r="C179" t="s">
@@ -12498,11 +12553,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>623</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="23" t="s">
         <v>624</v>
       </c>
       <c r="C180" t="s">
@@ -12524,11 +12579,11 @@
         <v>123</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>627</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="23" t="s">
         <v>628</v>
       </c>
       <c r="C181" t="s">
@@ -12550,11 +12605,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>631</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="23" t="s">
         <v>632</v>
       </c>
       <c r="C182" t="s">
@@ -12576,11 +12631,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>635</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" s="23" t="s">
         <v>636</v>
       </c>
       <c r="C183" t="s">
@@ -12602,11 +12657,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>639</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="23" t="s">
         <v>640</v>
       </c>
       <c r="C184" t="s">
@@ -12628,11 +12683,11 @@
         <v>102</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>643</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="23" t="s">
         <v>644</v>
       </c>
       <c r="C185" t="s">
@@ -12654,11 +12709,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>647</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="23" t="s">
         <v>648</v>
       </c>
       <c r="C186" t="s">
@@ -12680,11 +12735,11 @@
         <v>134</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>651</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="23" t="s">
         <v>652</v>
       </c>
       <c r="C187" t="s">
@@ -12706,11 +12761,11 @@
         <v>134</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>655</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="23" t="s">
         <v>656</v>
       </c>
       <c r="C188" t="s">
@@ -12732,11 +12787,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>659</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="23" t="s">
         <v>660</v>
       </c>
       <c r="C189" t="s">
@@ -12758,11 +12813,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>663</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" s="23" t="s">
         <v>664</v>
       </c>
       <c r="C190" t="s">
@@ -12784,11 +12839,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>667</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="23" t="s">
         <v>668</v>
       </c>
       <c r="C191" t="s">
@@ -12810,11 +12865,11 @@
         <v>108</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>671</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="23" t="s">
         <v>672</v>
       </c>
       <c r="C192" t="s">
@@ -12839,11 +12894,11 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>675</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="23" t="s">
         <v>676</v>
       </c>
       <c r="C193" t="s">
@@ -12865,11 +12920,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>679</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="23" t="s">
         <v>680</v>
       </c>
       <c r="C194" t="s">
@@ -12891,11 +12946,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>683</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="23" t="s">
         <v>684</v>
       </c>
       <c r="C195" t="s">
@@ -12917,11 +12972,11 @@
         <v>61</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>687</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="23" t="s">
         <v>688</v>
       </c>
       <c r="C196" t="s">
@@ -12943,11 +12998,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>691</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="23" t="s">
         <v>692</v>
       </c>
       <c r="C197" t="s">
@@ -12972,11 +13027,11 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>695</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" s="23" t="s">
         <v>696</v>
       </c>
       <c r="C198" t="s">
@@ -12998,11 +13053,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>699</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="23" t="s">
         <v>700</v>
       </c>
       <c r="C199" t="s">
@@ -13024,11 +13079,11 @@
         <v>89</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>703</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="23" t="s">
         <v>704</v>
       </c>
       <c r="C200" t="s">
@@ -13050,11 +13105,11 @@
         <v>98</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>707</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="23" t="s">
         <v>708</v>
       </c>
       <c r="C201" t="s">
@@ -13076,11 +13131,11 @@
         <v>76</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>711</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="23" t="s">
         <v>712</v>
       </c>
       <c r="C202" t="s">
@@ -13102,11 +13157,11 @@
         <v>70</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>715</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="23" t="s">
         <v>716</v>
       </c>
       <c r="C203" t="s">
@@ -13128,11 +13183,11 @@
         <v>133</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>719</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" s="23" t="s">
         <v>720</v>
       </c>
       <c r="C204" t="s">
@@ -13154,11 +13209,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>723</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="23" t="s">
         <v>724</v>
       </c>
       <c r="C205" t="s">
@@ -13180,11 +13235,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>727</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="23" t="s">
         <v>728</v>
       </c>
       <c r="C206" t="s">
@@ -13206,11 +13261,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>731</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="23" t="s">
         <v>732</v>
       </c>
       <c r="C207" t="s">
@@ -13232,11 +13287,11 @@
         <v>141</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>735</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="23" t="s">
         <v>736</v>
       </c>
       <c r="C208" t="s">
@@ -13258,11 +13313,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>5</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" s="23" t="s">
         <v>5</v>
       </c>
       <c r="C209" t="s">
@@ -13287,11 +13342,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>10</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B210" s="23" t="s">
         <v>10</v>
       </c>
       <c r="C210" t="s">
@@ -13316,11 +13371,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>14</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" s="23" t="s">
         <v>14</v>
       </c>
       <c r="C211" t="s">
@@ -13345,11 +13400,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>18</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B212" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C212" t="s">
@@ -13374,11 +13429,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>22</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="23" t="s">
         <v>22</v>
       </c>
       <c r="C213" t="s">
@@ -13403,11 +13458,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>26</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B214" s="23" t="s">
         <v>26</v>
       </c>
       <c r="C214" t="s">
@@ -13432,11 +13487,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>30</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="23" t="s">
         <v>30</v>
       </c>
       <c r="C215" t="s">
@@ -13461,11 +13516,11 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>34</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B216" s="23" t="s">
         <v>34</v>
       </c>
       <c r="C216" t="s">
@@ -13490,11 +13545,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>38</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B217" s="23" t="s">
         <v>38</v>
       </c>
       <c r="C217" t="s">
@@ -13519,11 +13574,11 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>42</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B218" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C218" t="s">
@@ -13548,11 +13603,11 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>46</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B219" s="23" t="s">
         <v>46</v>
       </c>
       <c r="C219" t="s">
@@ -13577,11 +13632,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>175</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B220" s="23" t="s">
         <v>175</v>
       </c>
       <c r="C220" t="s">
@@ -13606,11 +13661,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>50</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" s="23" t="s">
         <v>50</v>
       </c>
       <c r="C221" t="s">
@@ -13635,11 +13690,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>54</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" s="23" t="s">
         <v>54</v>
       </c>
       <c r="C222" t="s">
@@ -13664,11 +13719,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>58</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" s="23" t="s">
         <v>58</v>
       </c>
       <c r="C223" t="s">
@@ -13693,11 +13748,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>170</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="23" t="s">
         <v>739</v>
       </c>
       <c r="C224" t="s">
@@ -13719,11 +13774,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>740</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" s="23" t="s">
         <v>740</v>
       </c>
       <c r="C225" t="s">
@@ -13748,11 +13803,11 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>128</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" s="23" t="s">
         <v>128</v>
       </c>
       <c r="C226" t="s">
@@ -13774,11 +13829,11 @@
         <v>105</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>134</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="23" t="s">
         <v>134</v>
       </c>
       <c r="C227" t="s">
@@ -13800,11 +13855,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="B228" s="3" t="s">
+      <c r="B228" s="22" t="s">
         <v>742</v>
       </c>
       <c r="C228" s="3" t="s">
@@ -13829,11 +13884,11 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>744</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" s="23" t="s">
         <v>745</v>
       </c>
       <c r="C229" t="s">
@@ -13855,11 +13910,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>746</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" s="23" t="s">
         <v>747</v>
       </c>
       <c r="C230" t="s">
@@ -13881,11 +13936,11 @@
         <v>89</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>748</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="23" t="s">
         <v>749</v>
       </c>
       <c r="C231" t="s">
@@ -13907,11 +13962,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>750</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="23" t="s">
         <v>751</v>
       </c>
       <c r="C232" t="s">
@@ -13933,11 +13988,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>754</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="23" t="s">
         <v>755</v>
       </c>
       <c r="C233" t="s">
@@ -13959,11 +14014,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>758</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="23" t="s">
         <v>759</v>
       </c>
       <c r="C234" t="s">
@@ -13985,11 +14040,11 @@
         <v>62</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>762</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="23" t="s">
         <v>763</v>
       </c>
       <c r="C235" t="s">
@@ -14011,11 +14066,11 @@
         <v>101</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>766</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="23" t="s">
         <v>767</v>
       </c>
       <c r="C236" t="s">
@@ -14040,11 +14095,11 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>770</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" s="23" t="s">
         <v>771</v>
       </c>
       <c r="C237" t="s">
@@ -14066,11 +14121,11 @@
         <v>70</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>774</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B238" s="23" t="s">
         <v>775</v>
       </c>
       <c r="C238" t="s">
@@ -14092,11 +14147,11 @@
         <v>60</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>778</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B239" s="23" t="s">
         <v>779</v>
       </c>
       <c r="C239" t="s">
@@ -14121,11 +14176,11 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>782</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B240" s="23" t="s">
         <v>783</v>
       </c>
       <c r="C240" t="s">
@@ -14150,11 +14205,11 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>786</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B241" s="23" t="s">
         <v>787</v>
       </c>
       <c r="C241" t="s">
@@ -14176,11 +14231,11 @@
         <v>76</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>790</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B242" s="23" t="s">
         <v>791</v>
       </c>
       <c r="C242" t="s">
@@ -14202,11 +14257,11 @@
         <v>89</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>794</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B243" s="23" t="s">
         <v>795</v>
       </c>
       <c r="C243" t="s">
@@ -14228,11 +14283,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>798</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B244" s="23" t="s">
         <v>799</v>
       </c>
       <c r="C244" t="s">
@@ -14254,11 +14309,11 @@
         <v>118</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>802</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B245" s="23" t="s">
         <v>803</v>
       </c>
       <c r="C245" t="s">
@@ -14280,11 +14335,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>806</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" s="23" t="s">
         <v>807</v>
       </c>
       <c r="C246" t="s">
@@ -14306,11 +14361,11 @@
         <v>96</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>810</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B247" s="23" t="s">
         <v>811</v>
       </c>
       <c r="C247" t="s">
@@ -14332,11 +14387,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>83</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" s="23" t="s">
         <v>814</v>
       </c>
       <c r="C248" t="s">
@@ -14358,11 +14413,11 @@
         <v>95</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>817</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="23" t="s">
         <v>818</v>
       </c>
       <c r="C249" t="s">
@@ -14384,11 +14439,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>821</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" s="23" t="s">
         <v>822</v>
       </c>
       <c r="C250" t="s">
@@ -14410,11 +14465,11 @@
         <v>60</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>825</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" s="23" t="s">
         <v>826</v>
       </c>
       <c r="C251" t="s">
@@ -14436,11 +14491,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>829</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B252" s="23" t="s">
         <v>830</v>
       </c>
       <c r="C252" t="s">
@@ -14462,11 +14517,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>833</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B253" s="23" t="s">
         <v>834</v>
       </c>
       <c r="C253" t="s">
@@ -14491,11 +14546,11 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>837</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B254" s="23" t="s">
         <v>838</v>
       </c>
       <c r="C254" t="s">
@@ -14520,11 +14575,11 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>841</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B255" s="23" t="s">
         <v>842</v>
       </c>
       <c r="C255" t="s">
@@ -14546,11 +14601,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>845</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B256" s="23" t="s">
         <v>846</v>
       </c>
       <c r="C256" t="s">
@@ -14572,11 +14627,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>849</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" s="23" t="s">
         <v>850</v>
       </c>
       <c r="C257" t="s">
@@ -14598,11 +14653,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>853</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" s="23" t="s">
         <v>854</v>
       </c>
       <c r="C258" t="s">
@@ -14624,11 +14679,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>857</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" s="23" t="s">
         <v>858</v>
       </c>
       <c r="C259" t="s">
@@ -14650,11 +14705,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>861</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" s="23" t="s">
         <v>862</v>
       </c>
       <c r="C260" t="s">
@@ -14676,11 +14731,11 @@
         <v>70</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>865</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" s="23" t="s">
         <v>866</v>
       </c>
       <c r="C261" t="s">
@@ -14702,11 +14757,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>869</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B262" s="23" t="s">
         <v>870</v>
       </c>
       <c r="C262" t="s">
@@ -14728,11 +14783,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>873</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B263" s="23" t="s">
         <v>874</v>
       </c>
       <c r="C263" t="s">
@@ -14754,11 +14809,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>101</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B264" s="23" t="s">
         <v>877</v>
       </c>
       <c r="C264" t="s">
@@ -14783,11 +14838,11 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>880</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B265" s="23" t="s">
         <v>881</v>
       </c>
       <c r="C265" t="s">
@@ -14809,11 +14864,11 @@
         <v>95</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>80</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B266" s="23" t="s">
         <v>884</v>
       </c>
       <c r="C266" t="s">
@@ -14835,11 +14890,11 @@
         <v>122</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>887</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B267" s="23" t="s">
         <v>888</v>
       </c>
       <c r="C267" t="s">
@@ -14861,11 +14916,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>891</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B268" s="23" t="s">
         <v>892</v>
       </c>
       <c r="C268" t="s">
@@ -14887,11 +14942,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>895</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B269" s="23" t="s">
         <v>896</v>
       </c>
       <c r="C269" t="s">
@@ -14913,11 +14968,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>899</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B270" s="23" t="s">
         <v>900</v>
       </c>
       <c r="C270" t="s">
@@ -14939,11 +14994,11 @@
         <v>68</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>903</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B271" s="23" t="s">
         <v>904</v>
       </c>
       <c r="C271" t="s">
@@ -14965,11 +15020,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>907</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B272" s="23" t="s">
         <v>908</v>
       </c>
       <c r="C272" t="s">
@@ -14991,11 +15046,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>911</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B273" s="23" t="s">
         <v>912</v>
       </c>
       <c r="C273" t="s">
@@ -15017,11 +15072,11 @@
         <v>66</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>915</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B274" s="23" t="s">
         <v>916</v>
       </c>
       <c r="C274" t="s">
@@ -15043,11 +15098,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>919</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B275" s="23" t="s">
         <v>920</v>
       </c>
       <c r="C275" t="s">
@@ -15069,11 +15124,11 @@
         <v>120</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>923</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B276" s="23" t="s">
         <v>924</v>
       </c>
       <c r="C276" t="s">
@@ -15095,11 +15150,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>927</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B277" s="23" t="s">
         <v>928</v>
       </c>
       <c r="C277" t="s">
@@ -15121,11 +15176,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>931</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B278" s="23" t="s">
         <v>932</v>
       </c>
       <c r="C278" t="s">
@@ -15147,11 +15202,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>935</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B279" s="23" t="s">
         <v>936</v>
       </c>
       <c r="C279" t="s">
@@ -15176,11 +15231,11 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>939</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B280" s="23" t="s">
         <v>940</v>
       </c>
       <c r="C280" t="s">
@@ -15202,11 +15257,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>943</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B281" s="23" t="s">
         <v>944</v>
       </c>
       <c r="C281" t="s">
@@ -15228,11 +15283,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>947</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B282" s="23" t="s">
         <v>948</v>
       </c>
       <c r="C282" t="s">
@@ -15254,11 +15309,11 @@
         <v>69</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>951</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B283" s="23" t="s">
         <v>952</v>
       </c>
       <c r="C283" t="s">
@@ -15280,11 +15335,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>955</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B284" s="23" t="s">
         <v>956</v>
       </c>
       <c r="C284" t="s">
@@ -15306,11 +15361,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>959</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B285" s="23" t="s">
         <v>960</v>
       </c>
       <c r="C285" t="s">
@@ -15332,11 +15387,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>963</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B286" s="23" t="s">
         <v>964</v>
       </c>
       <c r="C286" t="s">
@@ -15361,11 +15416,11 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>967</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B287" s="23" t="s">
         <v>968</v>
       </c>
       <c r="C287" t="s">
@@ -15387,11 +15442,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>971</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B288" s="23" t="s">
         <v>972</v>
       </c>
       <c r="C288" t="s">
@@ -15413,11 +15468,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>975</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B289" s="23" t="s">
         <v>976</v>
       </c>
       <c r="C289" t="s">
@@ -15439,11 +15494,11 @@
         <v>63</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>979</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B290" s="23" t="s">
         <v>980</v>
       </c>
       <c r="C290" t="s">
@@ -15465,11 +15520,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>983</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B291" s="23" t="s">
         <v>171</v>
       </c>
       <c r="C291" t="s">
@@ -15491,11 +15546,11 @@
         <v>98</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>986</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B292" s="23" t="s">
         <v>987</v>
       </c>
       <c r="C292" t="s">
@@ -15517,11 +15572,11 @@
         <v>72</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>990</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B293" s="23" t="s">
         <v>991</v>
       </c>
       <c r="C293" t="s">
@@ -15543,11 +15598,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>994</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B294" s="23" t="s">
         <v>995</v>
       </c>
       <c r="C294" t="s">
@@ -15569,11 +15624,11 @@
         <v>66</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>998</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B295" s="23" t="s">
         <v>999</v>
       </c>
       <c r="C295" t="s">
@@ -15598,11 +15653,11 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1002</v>
       </c>
-      <c r="B296" t="s">
+      <c r="B296" s="23" t="s">
         <v>1003</v>
       </c>
       <c r="C296" t="s">
@@ -15624,11 +15679,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1006</v>
       </c>
-      <c r="B297" t="s">
+      <c r="B297" s="23" t="s">
         <v>1007</v>
       </c>
       <c r="C297" t="s">
@@ -15650,11 +15705,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1010</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B298" s="23" t="s">
         <v>1011</v>
       </c>
       <c r="C298" t="s">
@@ -15676,11 +15731,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1014</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B299" s="23" t="s">
         <v>1015</v>
       </c>
       <c r="C299" t="s">
@@ -15702,11 +15757,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1018</v>
       </c>
-      <c r="B300" t="s">
+      <c r="B300" s="23" t="s">
         <v>1019</v>
       </c>
       <c r="C300" t="s">
@@ -15728,11 +15783,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1022</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B301" s="23" t="s">
         <v>1023</v>
       </c>
       <c r="C301" t="s">
@@ -15754,11 +15809,11 @@
         <v>37</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1026</v>
       </c>
-      <c r="B302" t="s">
+      <c r="B302" s="23" t="s">
         <v>1027</v>
       </c>
       <c r="C302" t="s">
@@ -15780,11 +15835,11 @@
         <v>76</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1030</v>
       </c>
-      <c r="B303" t="s">
+      <c r="B303" s="23" t="s">
         <v>1031</v>
       </c>
       <c r="C303" t="s">
@@ -15806,11 +15861,11 @@
         <v>24</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>5</v>
       </c>
-      <c r="B304" t="s">
+      <c r="B304" s="23" t="s">
         <v>5</v>
       </c>
       <c r="C304" t="s">
@@ -15835,11 +15890,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>10</v>
       </c>
-      <c r="B305" t="s">
+      <c r="B305" s="23" t="s">
         <v>10</v>
       </c>
       <c r="C305" t="s">
@@ -15864,11 +15919,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>14</v>
       </c>
-      <c r="B306" t="s">
+      <c r="B306" s="23" t="s">
         <v>14</v>
       </c>
       <c r="C306" t="s">
@@ -15893,11 +15948,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>18</v>
       </c>
-      <c r="B307" t="s">
+      <c r="B307" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C307" t="s">
@@ -15922,11 +15977,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>22</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B308" s="23" t="s">
         <v>22</v>
       </c>
       <c r="C308" t="s">
@@ -15951,11 +16006,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>26</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B309" s="23" t="s">
         <v>26</v>
       </c>
       <c r="C309" t="s">
@@ -15980,11 +16035,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>30</v>
       </c>
-      <c r="B310" t="s">
+      <c r="B310" s="23" t="s">
         <v>30</v>
       </c>
       <c r="C310" t="s">
@@ -16009,11 +16064,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>34</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B311" s="23" t="s">
         <v>34</v>
       </c>
       <c r="C311" t="s">
@@ -16038,11 +16093,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>38</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B312" s="23" t="s">
         <v>38</v>
       </c>
       <c r="C312" t="s">
@@ -16067,11 +16122,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>42</v>
       </c>
-      <c r="B313" t="s">
+      <c r="B313" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C313" t="s">
@@ -16096,11 +16151,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>46</v>
       </c>
-      <c r="B314" t="s">
+      <c r="B314" s="23" t="s">
         <v>46</v>
       </c>
       <c r="C314" t="s">
@@ -16125,11 +16180,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>175</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B315" s="23" t="s">
         <v>175</v>
       </c>
       <c r="C315" t="s">
@@ -16154,11 +16209,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>50</v>
       </c>
-      <c r="B316" t="s">
+      <c r="B316" s="23" t="s">
         <v>50</v>
       </c>
       <c r="C316" t="s">
@@ -16183,11 +16238,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>54</v>
       </c>
-      <c r="B317" t="s">
+      <c r="B317" s="23" t="s">
         <v>54</v>
       </c>
       <c r="C317" t="s">
@@ -16212,11 +16267,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>58</v>
       </c>
-      <c r="B318" t="s">
+      <c r="B318" s="23" t="s">
         <v>58</v>
       </c>
       <c r="C318" t="s">
@@ -16241,11 +16296,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>170</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B319" s="23" t="s">
         <v>739</v>
       </c>
       <c r="C319" t="s">
@@ -16267,11 +16322,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>740</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B320" s="23" t="s">
         <v>740</v>
       </c>
       <c r="C320" t="s">
@@ -16296,11 +16351,11 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>128</v>
       </c>
-      <c r="B321" t="s">
+      <c r="B321" s="23" t="s">
         <v>128</v>
       </c>
       <c r="C321" t="s">
@@ -16322,11 +16377,11 @@
         <v>63</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>134</v>
       </c>
-      <c r="B322" t="s">
+      <c r="B322" s="23" t="s">
         <v>134</v>
       </c>
       <c r="C322" t="s">
@@ -16348,11 +16403,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
         <v>1034</v>
       </c>
-      <c r="B323" s="3" t="s">
+      <c r="B323" s="22" t="s">
         <v>1035</v>
       </c>
       <c r="C323" s="3" t="s">
@@ -16377,11 +16432,11 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1037</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B324" s="23" t="s">
         <v>1038</v>
       </c>
       <c r="C324" t="s">
@@ -16406,11 +16461,11 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1039</v>
       </c>
-      <c r="B325" t="s">
+      <c r="B325" s="23" t="s">
         <v>1040</v>
       </c>
       <c r="C325" t="s">
@@ -16432,11 +16487,11 @@
         <v>87</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1043</v>
       </c>
-      <c r="B326" t="s">
+      <c r="B326" s="23" t="s">
         <v>1044</v>
       </c>
       <c r="C326" t="s">
@@ -16458,11 +16513,11 @@
         <v>62</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1045</v>
       </c>
-      <c r="B327" t="s">
+      <c r="B327" s="23" t="s">
         <v>1046</v>
       </c>
       <c r="C327" t="s">
@@ -16484,11 +16539,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1049</v>
       </c>
-      <c r="B328" t="s">
+      <c r="B328" s="23" t="s">
         <v>1050</v>
       </c>
       <c r="C328" t="s">
@@ -16510,11 +16565,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1053</v>
       </c>
-      <c r="B329" t="s">
+      <c r="B329" s="23" t="s">
         <v>1054</v>
       </c>
       <c r="C329" t="s">
@@ -16536,11 +16591,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1057</v>
       </c>
-      <c r="B330" t="s">
+      <c r="B330" s="23" t="s">
         <v>1058</v>
       </c>
       <c r="C330" t="s">
@@ -16562,11 +16617,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>1061</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B331" s="23" t="s">
         <v>1062</v>
       </c>
       <c r="C331" t="s">
@@ -16588,11 +16643,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1065</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B332" s="23" t="s">
         <v>1066</v>
       </c>
       <c r="C332" t="s">
@@ -16617,11 +16672,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1069</v>
       </c>
-      <c r="B333" t="s">
+      <c r="B333" s="23" t="s">
         <v>1070</v>
       </c>
       <c r="C333" t="s">
@@ -16643,11 +16698,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1073</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B334" s="23" t="s">
         <v>1074</v>
       </c>
       <c r="C334" t="s">
@@ -16669,11 +16724,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1077</v>
       </c>
-      <c r="B335" t="s">
+      <c r="B335" s="23" t="s">
         <v>1078</v>
       </c>
       <c r="C335" t="s">
@@ -16695,11 +16750,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1081</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B336" s="23" t="s">
         <v>1082</v>
       </c>
       <c r="C336" t="s">
@@ -16721,11 +16776,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1085</v>
       </c>
-      <c r="B337" t="s">
+      <c r="B337" s="23" t="s">
         <v>1086</v>
       </c>
       <c r="C337" t="s">
@@ -16750,11 +16805,11 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1089</v>
       </c>
-      <c r="B338" t="s">
+      <c r="B338" s="23" t="s">
         <v>1090</v>
       </c>
       <c r="C338" t="s">
@@ -16776,11 +16831,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1093</v>
       </c>
-      <c r="B339" t="s">
+      <c r="B339" s="23" t="s">
         <v>1094</v>
       </c>
       <c r="C339" t="s">
@@ -16802,11 +16857,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1097</v>
       </c>
-      <c r="B340" t="s">
+      <c r="B340" s="23" t="s">
         <v>1098</v>
       </c>
       <c r="C340" t="s">
@@ -16831,11 +16886,11 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1101</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B341" s="23" t="s">
         <v>1102</v>
       </c>
       <c r="C341" t="s">
@@ -16860,11 +16915,11 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1105</v>
       </c>
-      <c r="B342" t="s">
+      <c r="B342" s="23" t="s">
         <v>1106</v>
       </c>
       <c r="C342" t="s">
@@ -16889,11 +16944,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1109</v>
       </c>
-      <c r="B343" t="s">
+      <c r="B343" s="23" t="s">
         <v>1110</v>
       </c>
       <c r="C343" t="s">
@@ -16918,11 +16973,11 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1113</v>
       </c>
-      <c r="B344" t="s">
+      <c r="B344" s="23" t="s">
         <v>1114</v>
       </c>
       <c r="C344" t="s">
@@ -16947,11 +17002,11 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1117</v>
       </c>
-      <c r="B345" t="s">
+      <c r="B345" s="23" t="s">
         <v>1118</v>
       </c>
       <c r="C345" t="s">
@@ -16973,11 +17028,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1121</v>
       </c>
-      <c r="B346" t="s">
+      <c r="B346" s="23" t="s">
         <v>1122</v>
       </c>
       <c r="C346" t="s">
@@ -16999,11 +17054,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1125</v>
       </c>
-      <c r="B347" t="s">
+      <c r="B347" s="23" t="s">
         <v>1126</v>
       </c>
       <c r="C347" t="s">
@@ -17025,11 +17080,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1129</v>
       </c>
-      <c r="B348" t="s">
+      <c r="B348" s="23" t="s">
         <v>1130</v>
       </c>
       <c r="C348" t="s">
@@ -17051,11 +17106,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1133</v>
       </c>
-      <c r="B349" t="s">
+      <c r="B349" s="23" t="s">
         <v>1134</v>
       </c>
       <c r="C349" t="s">
@@ -17077,11 +17132,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1137</v>
       </c>
-      <c r="B350" t="s">
+      <c r="B350" s="23" t="s">
         <v>1138</v>
       </c>
       <c r="C350" t="s">
@@ -17103,11 +17158,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1141</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B351" s="23" t="s">
         <v>1142</v>
       </c>
       <c r="C351" t="s">
@@ -17129,11 +17184,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1145</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B352" s="23" t="s">
         <v>1146</v>
       </c>
       <c r="C352" t="s">
@@ -17155,11 +17210,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1149</v>
       </c>
-      <c r="B353" t="s">
+      <c r="B353" s="23" t="s">
         <v>1150</v>
       </c>
       <c r="C353" t="s">
@@ -17181,11 +17236,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1153</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B354" s="23" t="s">
         <v>1154</v>
       </c>
       <c r="C354" t="s">
@@ -17207,11 +17262,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1157</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B355" s="23" t="s">
         <v>1158</v>
       </c>
       <c r="C355" t="s">
@@ -17233,11 +17288,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1161</v>
       </c>
-      <c r="B356" t="s">
+      <c r="B356" s="23" t="s">
         <v>1162</v>
       </c>
       <c r="C356" t="s">
@@ -17259,11 +17314,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1165</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B357" s="23" t="s">
         <v>1166</v>
       </c>
       <c r="C357" t="s">
@@ -17285,11 +17340,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1169</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B358" s="23" t="s">
         <v>1170</v>
       </c>
       <c r="C358" t="s">
@@ -17311,11 +17366,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1173</v>
       </c>
-      <c r="B359" t="s">
+      <c r="B359" s="23" t="s">
         <v>1174</v>
       </c>
       <c r="C359" t="s">
@@ -17337,11 +17392,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1177</v>
       </c>
-      <c r="B360" t="s">
+      <c r="B360" s="23" t="s">
         <v>1178</v>
       </c>
       <c r="C360" t="s">
@@ -17363,11 +17418,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1181</v>
       </c>
-      <c r="B361" t="s">
+      <c r="B361" s="23" t="s">
         <v>1182</v>
       </c>
       <c r="C361" t="s">
@@ -17389,11 +17444,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1185</v>
       </c>
-      <c r="B362" t="s">
+      <c r="B362" s="23" t="s">
         <v>1186</v>
       </c>
       <c r="C362" t="s">
@@ -17415,11 +17470,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1189</v>
       </c>
-      <c r="B363" t="s">
+      <c r="B363" s="23" t="s">
         <v>1190</v>
       </c>
       <c r="C363" t="s">
@@ -17441,11 +17496,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1193</v>
       </c>
-      <c r="B364" t="s">
+      <c r="B364" s="23" t="s">
         <v>1194</v>
       </c>
       <c r="C364" t="s">
@@ -17467,11 +17522,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1197</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B365" s="23" t="s">
         <v>1198</v>
       </c>
       <c r="C365" t="s">
@@ -17493,11 +17548,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1201</v>
       </c>
-      <c r="B366" t="s">
+      <c r="B366" s="23" t="s">
         <v>1202</v>
       </c>
       <c r="C366" t="s">
@@ -17519,11 +17574,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1205</v>
       </c>
-      <c r="B367" t="s">
+      <c r="B367" s="23" t="s">
         <v>1206</v>
       </c>
       <c r="C367" t="s">
@@ -17545,11 +17600,11 @@
         <v>37</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1209</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B368" s="23" t="s">
         <v>1210</v>
       </c>
       <c r="C368" t="s">
@@ -17571,11 +17626,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1213</v>
       </c>
-      <c r="B369" t="s">
+      <c r="B369" s="23" t="s">
         <v>1214</v>
       </c>
       <c r="C369" t="s">
@@ -17597,11 +17652,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1217</v>
       </c>
-      <c r="B370" t="s">
+      <c r="B370" s="23" t="s">
         <v>1218</v>
       </c>
       <c r="C370" t="s">
@@ -17623,11 +17678,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1221</v>
       </c>
-      <c r="B371" t="s">
+      <c r="B371" s="23" t="s">
         <v>1222</v>
       </c>
       <c r="C371" t="s">
@@ -17649,11 +17704,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1225</v>
       </c>
-      <c r="B372" t="s">
+      <c r="B372" s="23" t="s">
         <v>1226</v>
       </c>
       <c r="C372" t="s">
@@ -17675,11 +17730,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1229</v>
       </c>
-      <c r="B373" t="s">
+      <c r="B373" s="23" t="s">
         <v>1230</v>
       </c>
       <c r="C373" t="s">
@@ -17704,11 +17759,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1233</v>
       </c>
-      <c r="B374" t="s">
+      <c r="B374" s="23" t="s">
         <v>1234</v>
       </c>
       <c r="C374" t="s">
@@ -17733,11 +17788,11 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1237</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B375" s="23" t="s">
         <v>1238</v>
       </c>
       <c r="C375" t="s">
@@ -17759,11 +17814,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1241</v>
       </c>
-      <c r="B376" t="s">
+      <c r="B376" s="23" t="s">
         <v>1242</v>
       </c>
       <c r="C376" t="s">
@@ -17785,11 +17840,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1245</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B377" s="23" t="s">
         <v>1246</v>
       </c>
       <c r="C377" t="s">
@@ -17811,11 +17866,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1249</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B378" s="23" t="s">
         <v>1250</v>
       </c>
       <c r="C378" t="s">
@@ -17837,11 +17892,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>161</v>
       </c>
-      <c r="B379" t="s">
+      <c r="B379" s="23" t="s">
         <v>1253</v>
       </c>
       <c r="C379" t="s">
@@ -17863,11 +17918,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1255</v>
       </c>
-      <c r="B380" t="s">
+      <c r="B380" s="23" t="s">
         <v>1256</v>
       </c>
       <c r="C380" t="s">
@@ -17889,11 +17944,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1259</v>
       </c>
-      <c r="B381" t="s">
+      <c r="B381" s="23" t="s">
         <v>1260</v>
       </c>
       <c r="C381" t="s">
@@ -17915,11 +17970,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1263</v>
       </c>
-      <c r="B382" t="s">
+      <c r="B382" s="23" t="s">
         <v>1264</v>
       </c>
       <c r="C382" t="s">
@@ -17944,11 +17999,11 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1267</v>
       </c>
-      <c r="B383" t="s">
+      <c r="B383" s="23" t="s">
         <v>1268</v>
       </c>
       <c r="C383" t="s">
@@ -17973,11 +18028,11 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>122</v>
       </c>
-      <c r="B384" t="s">
+      <c r="B384" s="23" t="s">
         <v>1271</v>
       </c>
       <c r="C384" t="s">
@@ -17999,11 +18054,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1272</v>
       </c>
-      <c r="B385" t="s">
+      <c r="B385" s="23" t="s">
         <v>1273</v>
       </c>
       <c r="C385" t="s">
@@ -18028,11 +18083,11 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>128</v>
       </c>
-      <c r="B386" t="s">
+      <c r="B386" s="23" t="s">
         <v>1274</v>
       </c>
       <c r="C386" t="s">
@@ -18054,11 +18109,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>134</v>
       </c>
-      <c r="B387" t="s">
+      <c r="B387" s="23" t="s">
         <v>1275</v>
       </c>
       <c r="C387" t="s">
@@ -18080,11 +18135,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>741</v>
       </c>
-      <c r="B388" t="s">
+      <c r="B388" s="23" t="s">
         <v>1276</v>
       </c>
       <c r="C388" t="s">
@@ -18109,11 +18164,11 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>647</v>
       </c>
-      <c r="B389" t="s">
+      <c r="B389" s="23" t="s">
         <v>1277</v>
       </c>
       <c r="C389" t="s">
@@ -18135,11 +18190,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>715</v>
       </c>
-      <c r="B390" t="s">
+      <c r="B390" s="23" t="s">
         <v>1278</v>
       </c>
       <c r="C390" t="s">
@@ -18161,11 +18216,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>798</v>
       </c>
-      <c r="B391" t="s">
+      <c r="B391" s="23" t="s">
         <v>1279</v>
       </c>
       <c r="C391" t="s">
@@ -18187,11 +18242,11 @@
         <v>44</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>829</v>
       </c>
-      <c r="B392" t="s">
+      <c r="B392" s="23" t="s">
         <v>1280</v>
       </c>
       <c r="C392" t="s">
@@ -18213,11 +18268,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1281</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B393" s="23" t="s">
         <v>1282</v>
       </c>
       <c r="C393" t="s">
@@ -18239,11 +18294,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1285</v>
       </c>
-      <c r="B394" t="s">
+      <c r="B394" s="23" t="s">
         <v>1286</v>
       </c>
       <c r="C394" t="s">
@@ -18265,11 +18320,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1287</v>
       </c>
-      <c r="B395" t="s">
+      <c r="B395" s="23" t="s">
         <v>1288</v>
       </c>
       <c r="C395" t="s">
@@ -18291,11 +18346,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1289</v>
       </c>
-      <c r="B396" t="s">
+      <c r="B396" s="23" t="s">
         <v>1290</v>
       </c>
       <c r="C396" t="s">
@@ -18320,11 +18375,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1292</v>
       </c>
-      <c r="B397" t="s">
+      <c r="B397" s="23" t="s">
         <v>1293</v>
       </c>
       <c r="C397" t="s">
@@ -18349,11 +18404,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1296</v>
       </c>
-      <c r="B398" t="s">
+      <c r="B398" s="23" t="s">
         <v>1297</v>
       </c>
       <c r="C398" t="s">
@@ -18378,11 +18433,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1300</v>
       </c>
-      <c r="B399" t="s">
+      <c r="B399" s="23" t="s">
         <v>1301</v>
       </c>
       <c r="C399" t="s">
@@ -18407,11 +18462,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1304</v>
       </c>
-      <c r="B400" t="s">
+      <c r="B400" s="23" t="s">
         <v>1305</v>
       </c>
       <c r="C400" t="s">
@@ -18440,11 +18495,11 @@
         <v>477</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>170</v>
       </c>
-      <c r="B401" t="s">
+      <c r="B401" s="23" t="s">
         <v>171</v>
       </c>
       <c r="C401" t="s">
@@ -18466,11 +18521,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1308</v>
       </c>
-      <c r="B402" t="s">
+      <c r="B402" s="23" t="s">
         <v>1309</v>
       </c>
       <c r="C402" t="s">
@@ -18496,11 +18551,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>210</v>
       </c>
-      <c r="B403" t="s">
+      <c r="B403" s="23" t="s">
         <v>1310</v>
       </c>
       <c r="C403" t="s">
@@ -18522,11 +18577,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>50</v>
       </c>
-      <c r="B404" t="s">
+      <c r="B404" s="23" t="s">
         <v>51</v>
       </c>
       <c r="C404" t="s">
@@ -18551,11 +18606,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>54</v>
       </c>
-      <c r="B405" t="s">
+      <c r="B405" s="23" t="s">
         <v>55</v>
       </c>
       <c r="C405" t="s">
@@ -18580,11 +18635,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>58</v>
       </c>
-      <c r="B406" t="s">
+      <c r="B406" s="23" t="s">
         <v>59</v>
       </c>
       <c r="C406" t="s">
@@ -18609,11 +18664,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1311</v>
       </c>
-      <c r="B407" t="s">
+      <c r="B407" s="23" t="s">
         <v>1312</v>
       </c>
       <c r="C407" t="s">
@@ -18638,11 +18693,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1315</v>
       </c>
-      <c r="B408" t="s">
+      <c r="B408" s="23" t="s">
         <v>1316</v>
       </c>
       <c r="C408" t="s">
@@ -18667,11 +18722,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1319</v>
       </c>
-      <c r="B409" t="s">
+      <c r="B409" s="23" t="s">
         <v>1320</v>
       </c>
       <c r="C409" t="s">
@@ -18696,11 +18751,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1323</v>
       </c>
-      <c r="B410" t="s">
+      <c r="B410" s="23" t="s">
         <v>1324</v>
       </c>
       <c r="C410" t="s">
@@ -18725,11 +18780,11 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="411" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="5" t="s">
         <v>1327</v>
       </c>
-      <c r="B411" s="5" t="s">
+      <c r="B411" s="24" t="s">
         <v>1328</v>
       </c>
       <c r="C411" s="5" t="s">
@@ -18754,11 +18809,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="412" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
         <v>1331</v>
       </c>
-      <c r="B412" s="3" t="s">
+      <c r="B412" s="22" t="s">
         <v>1332</v>
       </c>
       <c r="C412" s="3" t="s">
@@ -18781,11 +18836,11 @@
       </c>
       <c r="I412" s="3"/>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1336</v>
       </c>
-      <c r="B413" t="s">
+      <c r="B413" s="23" t="s">
         <v>1337</v>
       </c>
       <c r="C413" t="s">
@@ -18809,11 +18864,11 @@
       <c r="I413" s="5"/>
       <c r="J413" s="5"/>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1340</v>
       </c>
-      <c r="B414" t="s">
+      <c r="B414" s="23" t="s">
         <v>1341</v>
       </c>
       <c r="C414" t="s">
@@ -18839,11 +18894,11 @@
       </c>
       <c r="J414" s="5"/>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1344</v>
       </c>
-      <c r="B415" t="s">
+      <c r="B415" s="23" t="s">
         <v>1345</v>
       </c>
       <c r="C415" t="s">
@@ -18867,11 +18922,11 @@
       <c r="I415" s="5"/>
       <c r="J415" s="5"/>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1348</v>
       </c>
-      <c r="B416" t="s">
+      <c r="B416" s="23" t="s">
         <v>1349</v>
       </c>
       <c r="C416" t="s">
@@ -18895,11 +18950,11 @@
       <c r="I416" s="5"/>
       <c r="J416" s="5"/>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1352</v>
       </c>
-      <c r="B417" t="s">
+      <c r="B417" s="23" t="s">
         <v>1353</v>
       </c>
       <c r="C417" t="s">
@@ -18923,11 +18978,11 @@
       <c r="I417" s="5"/>
       <c r="J417" s="5"/>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1356</v>
       </c>
-      <c r="B418" t="s">
+      <c r="B418" s="23" t="s">
         <v>1357</v>
       </c>
       <c r="C418" t="s">
@@ -18951,11 +19006,11 @@
       <c r="I418" s="5"/>
       <c r="J418" s="5"/>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1360</v>
       </c>
-      <c r="B419" t="s">
+      <c r="B419" s="23" t="s">
         <v>1361</v>
       </c>
       <c r="C419" t="s">
@@ -18981,11 +19036,11 @@
       </c>
       <c r="J419" s="5"/>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1364</v>
       </c>
-      <c r="B420" t="s">
+      <c r="B420" s="23" t="s">
         <v>1365</v>
       </c>
       <c r="C420" t="s">
@@ -19009,11 +19064,11 @@
       <c r="I420" s="5"/>
       <c r="J420" s="5"/>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1065</v>
       </c>
-      <c r="B421" t="s">
+      <c r="B421" s="23" t="s">
         <v>1368</v>
       </c>
       <c r="C421" t="s">
@@ -19039,11 +19094,11 @@
       </c>
       <c r="J421" s="5"/>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1371</v>
       </c>
-      <c r="B422" t="s">
+      <c r="B422" s="23" t="s">
         <v>1372</v>
       </c>
       <c r="C422" t="s">
@@ -19067,11 +19122,11 @@
       <c r="I422" s="5"/>
       <c r="J422" s="5"/>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1373</v>
       </c>
-      <c r="B423" t="s">
+      <c r="B423" s="23" t="s">
         <v>1374</v>
       </c>
       <c r="C423" t="s">
@@ -19095,11 +19150,11 @@
       <c r="I423" s="5"/>
       <c r="J423" s="5"/>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1377</v>
       </c>
-      <c r="B424" t="s">
+      <c r="B424" s="23" t="s">
         <v>1378</v>
       </c>
       <c r="C424" t="s">
@@ -19123,11 +19178,11 @@
       <c r="I424" s="5"/>
       <c r="J424" s="5"/>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1381</v>
       </c>
-      <c r="B425" t="s">
+      <c r="B425" s="23" t="s">
         <v>1382</v>
       </c>
       <c r="C425" t="s">
@@ -19153,11 +19208,11 @@
       </c>
       <c r="J425" s="5"/>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1385</v>
       </c>
-      <c r="B426" t="s">
+      <c r="B426" s="23" t="s">
         <v>1386</v>
       </c>
       <c r="C426" t="s">
@@ -19181,11 +19236,11 @@
       <c r="I426" s="5"/>
       <c r="J426" s="5"/>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1389</v>
       </c>
-      <c r="B427" t="s">
+      <c r="B427" s="23" t="s">
         <v>1390</v>
       </c>
       <c r="C427" t="s">
@@ -19211,11 +19266,11 @@
       </c>
       <c r="J427" s="5"/>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1105</v>
       </c>
-      <c r="B428" t="s">
+      <c r="B428" s="23" t="s">
         <v>1393</v>
       </c>
       <c r="C428" t="s">
@@ -19241,11 +19296,11 @@
       </c>
       <c r="J428" s="5"/>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1395</v>
       </c>
-      <c r="B429" t="s">
+      <c r="B429" s="23" t="s">
         <v>1396</v>
       </c>
       <c r="C429" t="s">
@@ -19269,11 +19324,11 @@
       <c r="I429" s="5"/>
       <c r="J429" s="5"/>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1399</v>
       </c>
-      <c r="B430" t="s">
+      <c r="B430" s="23" t="s">
         <v>1400</v>
       </c>
       <c r="C430" t="s">
@@ -19297,11 +19352,11 @@
       <c r="I430" s="5"/>
       <c r="J430" s="5"/>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1403</v>
       </c>
-      <c r="B431" t="s">
+      <c r="B431" s="23" t="s">
         <v>1404</v>
       </c>
       <c r="C431" t="s">
@@ -19325,11 +19380,11 @@
       <c r="I431" s="5"/>
       <c r="J431" s="5"/>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1407</v>
       </c>
-      <c r="B432" t="s">
+      <c r="B432" s="23" t="s">
         <v>1408</v>
       </c>
       <c r="C432" t="s">
@@ -19353,11 +19408,11 @@
       <c r="I432" s="5"/>
       <c r="J432" s="5"/>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>167</v>
       </c>
-      <c r="B433" t="s">
+      <c r="B433" s="23" t="s">
         <v>1410</v>
       </c>
       <c r="C433" t="s">
@@ -19381,11 +19436,11 @@
       <c r="I433" s="5"/>
       <c r="J433" s="5"/>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1413</v>
       </c>
-      <c r="B434" t="s">
+      <c r="B434" s="23" t="s">
         <v>1414</v>
       </c>
       <c r="C434" t="s">
@@ -19409,11 +19464,11 @@
       <c r="I434" s="5"/>
       <c r="J434" s="5"/>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1417</v>
       </c>
-      <c r="B435" t="s">
+      <c r="B435" s="23" t="s">
         <v>1418</v>
       </c>
       <c r="C435" t="s">
@@ -19437,11 +19492,11 @@
       <c r="I435" s="5"/>
       <c r="J435" s="5"/>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1081</v>
       </c>
-      <c r="B436" t="s">
+      <c r="B436" s="23" t="s">
         <v>1421</v>
       </c>
       <c r="C436" t="s">
@@ -19465,11 +19520,11 @@
       <c r="I436" s="5"/>
       <c r="J436" s="5"/>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1424</v>
       </c>
-      <c r="B437" t="s">
+      <c r="B437" s="23" t="s">
         <v>1425</v>
       </c>
       <c r="C437" t="s">
@@ -19495,11 +19550,11 @@
       </c>
       <c r="J437" s="5"/>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1428</v>
       </c>
-      <c r="B438" t="s">
+      <c r="B438" s="23" t="s">
         <v>1429</v>
       </c>
       <c r="C438" t="s">
@@ -19523,11 +19578,11 @@
       <c r="I438" s="5"/>
       <c r="J438" s="5"/>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1432</v>
       </c>
-      <c r="B439" t="s">
+      <c r="B439" s="23" t="s">
         <v>1433</v>
       </c>
       <c r="C439" t="s">
@@ -19553,11 +19608,11 @@
       </c>
       <c r="J439" s="5"/>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1436</v>
       </c>
-      <c r="B440" t="s">
+      <c r="B440" s="23" t="s">
         <v>1437</v>
       </c>
       <c r="C440" t="s">
@@ -19583,11 +19638,11 @@
       </c>
       <c r="J440" s="5"/>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1440</v>
       </c>
-      <c r="B441" t="s">
+      <c r="B441" s="23" t="s">
         <v>1441</v>
       </c>
       <c r="C441" t="s">
@@ -19611,11 +19666,11 @@
       <c r="I441" s="5"/>
       <c r="J441" s="5"/>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1444</v>
       </c>
-      <c r="B442" t="s">
+      <c r="B442" s="23" t="s">
         <v>1445</v>
       </c>
       <c r="C442" t="s">
@@ -19639,11 +19694,11 @@
       <c r="I442" s="5"/>
       <c r="J442" s="5"/>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1448</v>
       </c>
-      <c r="B443" t="s">
+      <c r="B443" s="23" t="s">
         <v>1449</v>
       </c>
       <c r="C443" t="s">
@@ -19667,11 +19722,11 @@
       <c r="I443" s="5"/>
       <c r="J443" s="5"/>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1452</v>
       </c>
-      <c r="B444" t="s">
+      <c r="B444" s="23" t="s">
         <v>1453</v>
       </c>
       <c r="C444" t="s">
@@ -19695,11 +19750,11 @@
       <c r="I444" s="5"/>
       <c r="J444" s="5"/>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1456</v>
       </c>
-      <c r="B445" t="s">
+      <c r="B445" s="23" t="s">
         <v>1457</v>
       </c>
       <c r="C445" t="s">
@@ -19723,11 +19778,11 @@
       <c r="I445" s="5"/>
       <c r="J445" s="5"/>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1460</v>
       </c>
-      <c r="B446" t="s">
+      <c r="B446" s="23" t="s">
         <v>1461</v>
       </c>
       <c r="C446" t="s">
@@ -19751,11 +19806,11 @@
       <c r="I446" s="5"/>
       <c r="J446" s="5"/>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1464</v>
       </c>
-      <c r="B447" t="s">
+      <c r="B447" s="23" t="s">
         <v>1465</v>
       </c>
       <c r="C447" t="s">
@@ -19779,11 +19834,11 @@
       <c r="I447" s="5"/>
       <c r="J447" s="5"/>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1468</v>
       </c>
-      <c r="B448" t="s">
+      <c r="B448" s="23" t="s">
         <v>1469</v>
       </c>
       <c r="C448" t="s">
@@ -19807,11 +19862,11 @@
       <c r="I448" s="5"/>
       <c r="J448" s="5"/>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1472</v>
       </c>
-      <c r="B449" t="s">
+      <c r="B449" s="23" t="s">
         <v>1473</v>
       </c>
       <c r="C449" t="s">
@@ -19835,11 +19890,11 @@
       <c r="I449" s="5"/>
       <c r="J449" s="5"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1476</v>
       </c>
-      <c r="B450" t="s">
+      <c r="B450" s="23" t="s">
         <v>1477</v>
       </c>
       <c r="C450" t="s">
@@ -19863,11 +19918,11 @@
       <c r="I450" s="5"/>
       <c r="J450" s="5"/>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1480</v>
       </c>
-      <c r="B451" t="s">
+      <c r="B451" s="23" t="s">
         <v>1481</v>
       </c>
       <c r="C451" t="s">
@@ -19891,11 +19946,11 @@
       <c r="I451" s="5"/>
       <c r="J451" s="5"/>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>1484</v>
       </c>
-      <c r="B452" t="s">
+      <c r="B452" s="23" t="s">
         <v>1485</v>
       </c>
       <c r="C452" t="s">
@@ -19919,11 +19974,11 @@
       <c r="I452" s="5"/>
       <c r="J452" s="5"/>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1488</v>
       </c>
-      <c r="B453" t="s">
+      <c r="B453" s="23" t="s">
         <v>1489</v>
       </c>
       <c r="C453" t="s">
@@ -19947,11 +20002,11 @@
       <c r="I453" s="5"/>
       <c r="J453" s="5"/>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>1492</v>
       </c>
-      <c r="B454" t="s">
+      <c r="B454" s="23" t="s">
         <v>1493</v>
       </c>
       <c r="C454" t="s">
@@ -19975,11 +20030,11 @@
       <c r="I454" s="5"/>
       <c r="J454" s="5"/>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>1496</v>
       </c>
-      <c r="B455" t="s">
+      <c r="B455" s="23" t="s">
         <v>1497</v>
       </c>
       <c r="C455" t="s">
@@ -20003,11 +20058,11 @@
       <c r="I455" s="5"/>
       <c r="J455" s="5"/>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>1500</v>
       </c>
-      <c r="B456" t="s">
+      <c r="B456" s="23" t="s">
         <v>1501</v>
       </c>
       <c r="C456" t="s">
@@ -20031,11 +20086,11 @@
       <c r="I456" s="5"/>
       <c r="J456" s="5"/>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>1504</v>
       </c>
-      <c r="B457" t="s">
+      <c r="B457" s="23" t="s">
         <v>1505</v>
       </c>
       <c r="C457" t="s">
@@ -20059,11 +20114,11 @@
       <c r="I457" s="5"/>
       <c r="J457" s="5"/>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1508</v>
       </c>
-      <c r="B458" t="s">
+      <c r="B458" s="23" t="s">
         <v>1509</v>
       </c>
       <c r="C458" t="s">
@@ -20087,11 +20142,11 @@
       <c r="I458" s="5"/>
       <c r="J458" s="5"/>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1511</v>
       </c>
-      <c r="B459" t="s">
+      <c r="B459" s="23" t="s">
         <v>1512</v>
       </c>
       <c r="C459" t="s">
@@ -20117,11 +20172,11 @@
       </c>
       <c r="J459" s="5"/>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1515</v>
       </c>
-      <c r="B460" t="s">
+      <c r="B460" s="23" t="s">
         <v>1516</v>
       </c>
       <c r="C460" t="s">
@@ -20145,11 +20200,11 @@
       <c r="I460" s="5"/>
       <c r="J460" s="5"/>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>1519</v>
       </c>
-      <c r="B461" t="s">
+      <c r="B461" s="23" t="s">
         <v>1520</v>
       </c>
       <c r="C461" t="s">
@@ -20173,11 +20228,11 @@
       <c r="I461" s="5"/>
       <c r="J461" s="5"/>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1523</v>
       </c>
-      <c r="B462" t="s">
+      <c r="B462" s="23" t="s">
         <v>1524</v>
       </c>
       <c r="C462" t="s">
@@ -20201,11 +20256,11 @@
       <c r="I462" s="5"/>
       <c r="J462" s="5"/>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>134</v>
       </c>
-      <c r="B463" t="s">
+      <c r="B463" s="23" t="s">
         <v>1275</v>
       </c>
       <c r="C463" t="s">
@@ -20229,11 +20284,11 @@
       <c r="I463" s="5"/>
       <c r="J463" s="5"/>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>741</v>
       </c>
-      <c r="B464" t="s">
+      <c r="B464" s="23" t="s">
         <v>1276</v>
       </c>
       <c r="C464" t="s">
@@ -20259,11 +20314,11 @@
       </c>
       <c r="J464" s="5"/>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>647</v>
       </c>
-      <c r="B465" t="s">
+      <c r="B465" s="23" t="s">
         <v>1277</v>
       </c>
       <c r="C465" t="s">
@@ -20287,11 +20342,11 @@
       <c r="I465" s="5"/>
       <c r="J465" s="5"/>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>715</v>
       </c>
-      <c r="B466" t="s">
+      <c r="B466" s="23" t="s">
         <v>1278</v>
       </c>
       <c r="C466" t="s">
@@ -20315,11 +20370,11 @@
       <c r="I466" s="5"/>
       <c r="J466" s="5"/>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>798</v>
       </c>
-      <c r="B467" t="s">
+      <c r="B467" s="23" t="s">
         <v>1279</v>
       </c>
       <c r="C467" t="s">
@@ -20343,11 +20398,11 @@
       <c r="I467" s="5"/>
       <c r="J467" s="5"/>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>829</v>
       </c>
-      <c r="B468" t="s">
+      <c r="B468" s="23" t="s">
         <v>1280</v>
       </c>
       <c r="C468" t="s">
@@ -20371,11 +20426,11 @@
       <c r="I468" s="5"/>
       <c r="J468" s="5"/>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1281</v>
       </c>
-      <c r="B469" t="s">
+      <c r="B469" s="23" t="s">
         <v>1282</v>
       </c>
       <c r="C469" t="s">
@@ -20401,11 +20456,11 @@
       </c>
       <c r="J469" s="5"/>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1285</v>
       </c>
-      <c r="B470" t="s">
+      <c r="B470" s="23" t="s">
         <v>1286</v>
       </c>
       <c r="C470" t="s">
@@ -20429,11 +20484,11 @@
       <c r="I470" s="5"/>
       <c r="J470" s="5"/>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1287</v>
       </c>
-      <c r="B471" t="s">
+      <c r="B471" s="23" t="s">
         <v>1288</v>
       </c>
       <c r="C471" t="s">
@@ -20457,11 +20512,11 @@
       <c r="I471" s="5"/>
       <c r="J471" s="5"/>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1289</v>
       </c>
-      <c r="B472" t="s">
+      <c r="B472" s="23" t="s">
         <v>1290</v>
       </c>
       <c r="C472" t="s">
@@ -20487,11 +20542,11 @@
       </c>
       <c r="J472" s="5"/>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1292</v>
       </c>
-      <c r="B473" t="s">
+      <c r="B473" s="23" t="s">
         <v>1293</v>
       </c>
       <c r="C473" t="s">
@@ -20517,11 +20572,11 @@
       </c>
       <c r="J473" s="5"/>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1296</v>
       </c>
-      <c r="B474" t="s">
+      <c r="B474" s="23" t="s">
         <v>1297</v>
       </c>
       <c r="C474" t="s">
@@ -20547,11 +20602,11 @@
       </c>
       <c r="J474" s="5"/>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>5</v>
       </c>
-      <c r="B475" t="s">
+      <c r="B475" s="23" t="s">
         <v>6</v>
       </c>
       <c r="C475" t="s">
@@ -20577,11 +20632,11 @@
       </c>
       <c r="J475" s="5"/>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>10</v>
       </c>
-      <c r="B476" t="s">
+      <c r="B476" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C476" t="s">
@@ -20607,11 +20662,11 @@
       </c>
       <c r="J476" s="5"/>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>14</v>
       </c>
-      <c r="B477" t="s">
+      <c r="B477" s="23" t="s">
         <v>15</v>
       </c>
       <c r="C477" t="s">
@@ -20637,11 +20692,11 @@
       </c>
       <c r="J477" s="5"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>18</v>
       </c>
-      <c r="B478" t="s">
+      <c r="B478" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C478" t="s">
@@ -20667,11 +20722,11 @@
       </c>
       <c r="J478" s="5"/>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>22</v>
       </c>
-      <c r="B479" t="s">
+      <c r="B479" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C479" t="s">
@@ -20697,11 +20752,11 @@
       </c>
       <c r="J479" s="5"/>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>26</v>
       </c>
-      <c r="B480" t="s">
+      <c r="B480" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C480" t="s">
@@ -20727,11 +20782,11 @@
       </c>
       <c r="J480" s="5"/>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>30</v>
       </c>
-      <c r="B481" t="s">
+      <c r="B481" s="23" t="s">
         <v>31</v>
       </c>
       <c r="C481" t="s">
@@ -20757,11 +20812,11 @@
       </c>
       <c r="J481" s="5"/>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>34</v>
       </c>
-      <c r="B482" t="s">
+      <c r="B482" s="23" t="s">
         <v>35</v>
       </c>
       <c r="C482" t="s">
@@ -20787,11 +20842,11 @@
       </c>
       <c r="J482" s="5"/>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>38</v>
       </c>
-      <c r="B483" t="s">
+      <c r="B483" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C483" t="s">
@@ -20817,11 +20872,11 @@
       </c>
       <c r="J483" s="5"/>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>42</v>
       </c>
-      <c r="B484" t="s">
+      <c r="B484" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C484" t="s">
@@ -20847,11 +20902,11 @@
       </c>
       <c r="J484" s="5"/>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>46</v>
       </c>
-      <c r="B485" t="s">
+      <c r="B485" s="23" t="s">
         <v>47</v>
       </c>
       <c r="C485" t="s">
@@ -20877,11 +20932,11 @@
       </c>
       <c r="J485" s="5"/>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>175</v>
       </c>
-      <c r="B486" t="s">
+      <c r="B486" s="23" t="s">
         <v>176</v>
       </c>
       <c r="C486" t="s">
@@ -20907,11 +20962,11 @@
       </c>
       <c r="J486" s="5"/>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>54</v>
       </c>
-      <c r="B487" t="s">
+      <c r="B487" s="23" t="s">
         <v>55</v>
       </c>
       <c r="C487" t="s">
@@ -20937,11 +20992,11 @@
       </c>
       <c r="J487" s="5"/>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>58</v>
       </c>
-      <c r="B488" t="s">
+      <c r="B488" s="23" t="s">
         <v>59</v>
       </c>
       <c r="C488" t="s">
@@ -20967,11 +21022,11 @@
       </c>
       <c r="J488" s="5"/>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>1311</v>
       </c>
-      <c r="B489" t="s">
+      <c r="B489" s="23" t="s">
         <v>1312</v>
       </c>
       <c r="C489" t="s">
@@ -20997,11 +21052,11 @@
       </c>
       <c r="J489" s="5"/>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1315</v>
       </c>
-      <c r="B490" t="s">
+      <c r="B490" s="23" t="s">
         <v>1316</v>
       </c>
       <c r="C490" t="s">
@@ -21027,11 +21082,11 @@
       </c>
       <c r="J490" s="5"/>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>1319</v>
       </c>
-      <c r="B491" t="s">
+      <c r="B491" s="23" t="s">
         <v>1320</v>
       </c>
       <c r="C491" t="s">
@@ -21057,11 +21112,11 @@
       </c>
       <c r="J491" s="5"/>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>1323</v>
       </c>
-      <c r="B492" t="s">
+      <c r="B492" s="23" t="s">
         <v>1324</v>
       </c>
       <c r="C492" t="s">
@@ -21087,11 +21142,11 @@
       </c>
       <c r="J492" s="5"/>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>1327</v>
       </c>
-      <c r="B493" t="s">
+      <c r="B493" s="23" t="s">
         <v>1328</v>
       </c>
       <c r="C493" t="s">
@@ -21117,11 +21172,11 @@
       </c>
       <c r="J493" s="5"/>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>1527</v>
       </c>
-      <c r="B494" t="s">
+      <c r="B494" s="23" t="s">
         <v>1528</v>
       </c>
       <c r="C494" t="s">
@@ -21147,11 +21202,11 @@
       </c>
       <c r="J494" s="5"/>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1531</v>
       </c>
-      <c r="B495" t="s">
+      <c r="B495" s="23" t="s">
         <v>1532</v>
       </c>
       <c r="C495" t="s">
@@ -21177,11 +21232,11 @@
       </c>
       <c r="J495" s="5"/>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A496" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B496" s="3" t="s">
+      <c r="B496" s="22" t="s">
         <v>1535</v>
       </c>
       <c r="C496" s="3" t="s">
@@ -21204,11 +21259,11 @@
       </c>
       <c r="I496" s="3"/>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>611</v>
       </c>
-      <c r="B497" t="s">
+      <c r="B497" s="23" t="s">
         <v>1539</v>
       </c>
       <c r="C497" t="s">
@@ -21230,11 +21285,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>723</v>
       </c>
-      <c r="B498" t="s">
+      <c r="B498" s="23" t="s">
         <v>1542</v>
       </c>
       <c r="C498" t="s">
@@ -21259,11 +21314,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1545</v>
       </c>
-      <c r="B499" t="s">
+      <c r="B499" s="23" t="s">
         <v>1546</v>
       </c>
       <c r="C499" t="s">
@@ -21285,11 +21340,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>1549</v>
       </c>
-      <c r="B500" t="s">
+      <c r="B500" s="23" t="s">
         <v>1550</v>
       </c>
       <c r="C500" t="s">
@@ -21311,11 +21366,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>1553</v>
       </c>
-      <c r="B501" t="s">
+      <c r="B501" s="23" t="s">
         <v>1554</v>
       </c>
       <c r="C501" t="s">
@@ -21337,11 +21392,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>1557</v>
       </c>
-      <c r="B502" t="s">
+      <c r="B502" s="23" t="s">
         <v>1558</v>
       </c>
       <c r="C502" t="s">
@@ -21363,11 +21418,11 @@
         <v>36</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>1561</v>
       </c>
-      <c r="B503" t="s">
+      <c r="B503" s="23" t="s">
         <v>1562</v>
       </c>
       <c r="C503" t="s">
@@ -21392,11 +21447,11 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>1043</v>
       </c>
-      <c r="B504" t="s">
+      <c r="B504" s="23" t="s">
         <v>1565</v>
       </c>
       <c r="C504" t="s">
@@ -21418,11 +21473,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>1568</v>
       </c>
-      <c r="B505" t="s">
+      <c r="B505" s="23" t="s">
         <v>1569</v>
       </c>
       <c r="C505" t="s">
@@ -21444,11 +21499,11 @@
         <v>165</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>1572</v>
       </c>
-      <c r="B506" t="s">
+      <c r="B506" s="23" t="s">
         <v>1573</v>
       </c>
       <c r="C506" t="s">
@@ -21470,11 +21525,11 @@
         <v>68</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>1576</v>
       </c>
-      <c r="B507" t="s">
+      <c r="B507" s="23" t="s">
         <v>1577</v>
       </c>
       <c r="C507" t="s">
@@ -21496,11 +21551,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>1580</v>
       </c>
-      <c r="B508" t="s">
+      <c r="B508" s="23" t="s">
         <v>1581</v>
       </c>
       <c r="C508" t="s">
@@ -21522,11 +21577,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>1582</v>
       </c>
-      <c r="B509" t="s">
+      <c r="B509" s="23" t="s">
         <v>1583</v>
       </c>
       <c r="C509" t="s">
@@ -21548,11 +21603,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>1586</v>
       </c>
-      <c r="B510" t="s">
+      <c r="B510" s="23" t="s">
         <v>1587</v>
       </c>
       <c r="C510" t="s">
@@ -21574,11 +21629,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>1590</v>
       </c>
-      <c r="B511" t="s">
+      <c r="B511" s="23" t="s">
         <v>1591</v>
       </c>
       <c r="C511" t="s">
@@ -21600,11 +21655,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>1592</v>
       </c>
-      <c r="B512" t="s">
+      <c r="B512" s="23" t="s">
         <v>1593</v>
       </c>
       <c r="C512" t="s">
@@ -21626,11 +21681,11 @@
         <v>19</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>1596</v>
       </c>
-      <c r="B513" t="s">
+      <c r="B513" s="23" t="s">
         <v>1597</v>
       </c>
       <c r="C513" t="s">
@@ -21652,11 +21707,11 @@
         <v>70</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>1598</v>
       </c>
-      <c r="B514" t="s">
+      <c r="B514" s="23" t="s">
         <v>1599</v>
       </c>
       <c r="C514" t="s">
@@ -21678,11 +21733,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>1602</v>
       </c>
-      <c r="B515" t="s">
+      <c r="B515" s="23" t="s">
         <v>1603</v>
       </c>
       <c r="C515" t="s">
@@ -21704,11 +21759,11 @@
         <v>87</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>1606</v>
       </c>
-      <c r="B516" t="s">
+      <c r="B516" s="23" t="s">
         <v>1607</v>
       </c>
       <c r="C516" t="s">
@@ -21730,11 +21785,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>1610</v>
       </c>
-      <c r="B517" t="s">
+      <c r="B517" s="23" t="s">
         <v>1611</v>
       </c>
       <c r="C517" t="s">
@@ -21756,11 +21811,11 @@
         <v>112</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>1614</v>
       </c>
-      <c r="B518" t="s">
+      <c r="B518" s="23" t="s">
         <v>1615</v>
       </c>
       <c r="C518" t="s">
@@ -21782,11 +21837,11 @@
         <v>87</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>1618</v>
       </c>
-      <c r="B519" t="s">
+      <c r="B519" s="23" t="s">
         <v>1619</v>
       </c>
       <c r="C519" t="s">
@@ -21808,11 +21863,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>1622</v>
       </c>
-      <c r="B520" t="s">
+      <c r="B520" s="23" t="s">
         <v>1623</v>
       </c>
       <c r="C520" t="s">
@@ -21834,11 +21889,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>1626</v>
       </c>
-      <c r="B521" t="s">
+      <c r="B521" s="23" t="s">
         <v>1627</v>
       </c>
       <c r="C521" t="s">
@@ -21863,11 +21918,11 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>1630</v>
       </c>
-      <c r="B522" t="s">
+      <c r="B522" s="23" t="s">
         <v>1631</v>
       </c>
       <c r="C522" t="s">
@@ -21889,11 +21944,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>1634</v>
       </c>
-      <c r="B523" t="s">
+      <c r="B523" s="23" t="s">
         <v>1635</v>
       </c>
       <c r="C523" t="s">
@@ -21915,11 +21970,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>1638</v>
       </c>
-      <c r="B524" t="s">
+      <c r="B524" s="23" t="s">
         <v>1639</v>
       </c>
       <c r="C524" t="s">
@@ -21941,11 +21996,11 @@
         <v>19</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>1642</v>
       </c>
-      <c r="B525" t="s">
+      <c r="B525" s="23" t="s">
         <v>1643</v>
       </c>
       <c r="C525" t="s">
@@ -21967,11 +22022,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>1646</v>
       </c>
-      <c r="B526" t="s">
+      <c r="B526" s="23" t="s">
         <v>1647</v>
       </c>
       <c r="C526" t="s">
@@ -21996,11 +22051,11 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>1650</v>
       </c>
-      <c r="B527" t="s">
+      <c r="B527" s="23" t="s">
         <v>1651</v>
       </c>
       <c r="C527" t="s">
@@ -22022,11 +22077,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>1654</v>
       </c>
-      <c r="B528" t="s">
+      <c r="B528" s="23" t="s">
         <v>1655</v>
       </c>
       <c r="C528" t="s">
@@ -22051,11 +22106,11 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>1658</v>
       </c>
-      <c r="B529" t="s">
+      <c r="B529" s="23" t="s">
         <v>1659</v>
       </c>
       <c r="C529" t="s">
@@ -22080,11 +22135,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>1662</v>
       </c>
-      <c r="B530" t="s">
+      <c r="B530" s="23" t="s">
         <v>1663</v>
       </c>
       <c r="C530" t="s">
@@ -22106,11 +22161,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>1666</v>
       </c>
-      <c r="B531" t="s">
+      <c r="B531" s="23" t="s">
         <v>1667</v>
       </c>
       <c r="C531" t="s">
@@ -22135,11 +22190,11 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>1670</v>
       </c>
-      <c r="B532" t="s">
+      <c r="B532" s="23" t="s">
         <v>1671</v>
       </c>
       <c r="C532" t="s">
@@ -22161,11 +22216,11 @@
         <v>62</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>1674</v>
       </c>
-      <c r="B533" t="s">
+      <c r="B533" s="23" t="s">
         <v>1675</v>
       </c>
       <c r="C533" t="s">
@@ -22187,11 +22242,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>1678</v>
       </c>
-      <c r="B534" t="s">
+      <c r="B534" s="23" t="s">
         <v>1679</v>
       </c>
       <c r="C534" t="s">
@@ -22213,11 +22268,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>1682</v>
       </c>
-      <c r="B535" t="s">
+      <c r="B535" s="23" t="s">
         <v>1683</v>
       </c>
       <c r="C535" t="s">
@@ -22239,11 +22294,11 @@
         <v>19</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>1684</v>
       </c>
-      <c r="B536" t="s">
+      <c r="B536" s="23" t="s">
         <v>1685</v>
       </c>
       <c r="C536" t="s">
@@ -22265,11 +22320,11 @@
         <v>72</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>1688</v>
       </c>
-      <c r="B537" t="s">
+      <c r="B537" s="23" t="s">
         <v>1689</v>
       </c>
       <c r="C537" t="s">
@@ -22291,11 +22346,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>1692</v>
       </c>
-      <c r="B538" t="s">
+      <c r="B538" s="23" t="s">
         <v>1693</v>
       </c>
       <c r="C538" t="s">
@@ -22320,11 +22375,11 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>1696</v>
       </c>
-      <c r="B539" t="s">
+      <c r="B539" s="23" t="s">
         <v>1697</v>
       </c>
       <c r="C539" t="s">
@@ -22346,11 +22401,11 @@
         <v>76</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>1700</v>
       </c>
-      <c r="B540" t="s">
+      <c r="B540" s="23" t="s">
         <v>1701</v>
       </c>
       <c r="C540" t="s">
@@ -22372,11 +22427,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>1704</v>
       </c>
-      <c r="B541" t="s">
+      <c r="B541" s="23" t="s">
         <v>1705</v>
       </c>
       <c r="C541" t="s">
@@ -22398,11 +22453,11 @@
         <v>37</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>1708</v>
       </c>
-      <c r="B542" t="s">
+      <c r="B542" s="23" t="s">
         <v>1709</v>
       </c>
       <c r="C542" t="s">
@@ -22424,11 +22479,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>1712</v>
       </c>
-      <c r="B543" t="s">
+      <c r="B543" s="23" t="s">
         <v>1713</v>
       </c>
       <c r="C543" t="s">
@@ -22450,11 +22505,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>1716</v>
       </c>
-      <c r="B544" t="s">
+      <c r="B544" s="23" t="s">
         <v>1717</v>
       </c>
       <c r="C544" t="s">
@@ -22476,11 +22531,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>1720</v>
       </c>
-      <c r="B545" t="s">
+      <c r="B545" s="23" t="s">
         <v>1721</v>
       </c>
       <c r="C545" t="s">
@@ -22502,11 +22557,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>1724</v>
       </c>
-      <c r="B546" t="s">
+      <c r="B546" s="23" t="s">
         <v>1725</v>
       </c>
       <c r="C546" t="s">
@@ -22531,11 +22586,11 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>1726</v>
       </c>
-      <c r="B547" t="s">
+      <c r="B547" s="23" t="s">
         <v>1727</v>
       </c>
       <c r="C547" t="s">
@@ -22557,11 +22612,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>1730</v>
       </c>
-      <c r="B548" t="s">
+      <c r="B548" s="23" t="s">
         <v>1731</v>
       </c>
       <c r="C548" t="s">
@@ -22586,11 +22641,11 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>1734</v>
       </c>
-      <c r="B549" t="s">
+      <c r="B549" s="23" t="s">
         <v>1735</v>
       </c>
       <c r="C549" t="s">
@@ -22615,11 +22670,11 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>1738</v>
       </c>
-      <c r="B550" t="s">
+      <c r="B550" s="23" t="s">
         <v>1739</v>
       </c>
       <c r="C550" t="s">
@@ -22644,11 +22699,11 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>1742</v>
       </c>
-      <c r="B551" t="s">
+      <c r="B551" s="23" t="s">
         <v>1743</v>
       </c>
       <c r="C551" t="s">
@@ -22670,11 +22725,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>1746</v>
       </c>
-      <c r="B552" t="s">
+      <c r="B552" s="23" t="s">
         <v>1747</v>
       </c>
       <c r="C552" t="s">
@@ -22696,11 +22751,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>1750</v>
       </c>
-      <c r="B553" t="s">
+      <c r="B553" s="23" t="s">
         <v>1751</v>
       </c>
       <c r="C553" t="s">
@@ -22722,11 +22777,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>1754</v>
       </c>
-      <c r="B554" t="s">
+      <c r="B554" s="23" t="s">
         <v>1755</v>
       </c>
       <c r="C554" t="s">
@@ -22751,11 +22806,11 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>1308</v>
       </c>
-      <c r="B555" t="s">
+      <c r="B555" s="23" t="s">
         <v>1758</v>
       </c>
       <c r="C555" t="s">
@@ -22777,11 +22832,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>1761</v>
       </c>
-      <c r="B556" t="s">
+      <c r="B556" s="23" t="s">
         <v>1762</v>
       </c>
       <c r="C556" t="s">
@@ -22803,11 +22858,11 @@
         <v>62</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>1765</v>
       </c>
-      <c r="B557" t="s">
+      <c r="B557" s="23" t="s">
         <v>1766</v>
       </c>
       <c r="C557" t="s">
@@ -22829,11 +22884,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>1769</v>
       </c>
-      <c r="B558" t="s">
+      <c r="B558" s="23" t="s">
         <v>1770</v>
       </c>
       <c r="C558" t="s">
@@ -22855,11 +22910,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>1773</v>
       </c>
-      <c r="B559" t="s">
+      <c r="B559" s="23" t="s">
         <v>1774</v>
       </c>
       <c r="C559" t="s">
@@ -22881,11 +22936,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>1777</v>
       </c>
-      <c r="B560" t="s">
+      <c r="B560" s="23" t="s">
         <v>1778</v>
       </c>
       <c r="C560" t="s">
@@ -22907,11 +22962,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>1781</v>
       </c>
-      <c r="B561" t="s">
+      <c r="B561" s="23" t="s">
         <v>1782</v>
       </c>
       <c r="C561" t="s">
@@ -22933,11 +22988,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>1785</v>
       </c>
-      <c r="B562" t="s">
+      <c r="B562" s="23" t="s">
         <v>1786</v>
       </c>
       <c r="C562" t="s">
@@ -22959,11 +23014,11 @@
         <v>24</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>1789</v>
       </c>
-      <c r="B563" t="s">
+      <c r="B563" s="23" t="s">
         <v>1790</v>
       </c>
       <c r="C563" t="s">
@@ -22985,11 +23040,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>1793</v>
       </c>
-      <c r="B564" t="s">
+      <c r="B564" s="23" t="s">
         <v>1794</v>
       </c>
       <c r="C564" t="s">
@@ -23011,11 +23066,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>5</v>
       </c>
-      <c r="B565" t="s">
+      <c r="B565" s="23" t="s">
         <v>6</v>
       </c>
       <c r="C565" t="s">
@@ -23040,11 +23095,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>10</v>
       </c>
-      <c r="B566" t="s">
+      <c r="B566" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C566" t="s">
@@ -23069,11 +23124,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>14</v>
       </c>
-      <c r="B567" t="s">
+      <c r="B567" s="23" t="s">
         <v>15</v>
       </c>
       <c r="C567" t="s">
@@ -23098,11 +23153,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>18</v>
       </c>
-      <c r="B568" t="s">
+      <c r="B568" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C568" t="s">
@@ -23127,11 +23182,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>22</v>
       </c>
-      <c r="B569" t="s">
+      <c r="B569" s="23" t="s">
         <v>23</v>
       </c>
       <c r="C569" t="s">
@@ -23156,11 +23211,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>26</v>
       </c>
-      <c r="B570" t="s">
+      <c r="B570" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C570" t="s">
@@ -23185,11 +23240,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>30</v>
       </c>
-      <c r="B571" t="s">
+      <c r="B571" s="23" t="s">
         <v>31</v>
       </c>
       <c r="C571" t="s">
@@ -23214,11 +23269,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>34</v>
       </c>
-      <c r="B572" t="s">
+      <c r="B572" s="23" t="s">
         <v>35</v>
       </c>
       <c r="C572" t="s">
@@ -23243,11 +23298,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>38</v>
       </c>
-      <c r="B573" t="s">
+      <c r="B573" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C573" t="s">
@@ -23272,11 +23327,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>42</v>
       </c>
-      <c r="B574" t="s">
+      <c r="B574" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C574" t="s">
@@ -23301,11 +23356,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>46</v>
       </c>
-      <c r="B575" t="s">
+      <c r="B575" s="23" t="s">
         <v>47</v>
       </c>
       <c r="C575" t="s">
@@ -23330,11 +23385,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>175</v>
       </c>
-      <c r="B576" t="s">
+      <c r="B576" s="23" t="s">
         <v>176</v>
       </c>
       <c r="C576" t="s">
@@ -23359,11 +23414,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>54</v>
       </c>
-      <c r="B577" t="s">
+      <c r="B577" s="23" t="s">
         <v>55</v>
       </c>
       <c r="C577" t="s">
@@ -23388,11 +23443,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>58</v>
       </c>
-      <c r="B578" t="s">
+      <c r="B578" s="23" t="s">
         <v>59</v>
       </c>
       <c r="C578" t="s">
@@ -23417,11 +23472,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>1311</v>
       </c>
-      <c r="B579" t="s">
+      <c r="B579" s="23" t="s">
         <v>1312</v>
       </c>
       <c r="C579" t="s">
@@ -23446,11 +23501,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>1315</v>
       </c>
-      <c r="B580" t="s">
+      <c r="B580" s="23" t="s">
         <v>1316</v>
       </c>
       <c r="C580" t="s">
@@ -23475,11 +23530,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>1319</v>
       </c>
-      <c r="B581" t="s">
+      <c r="B581" s="23" t="s">
         <v>1320</v>
       </c>
       <c r="C581" t="s">
@@ -23504,11 +23559,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>1323</v>
       </c>
-      <c r="B582" t="s">
+      <c r="B582" s="23" t="s">
         <v>1324</v>
       </c>
       <c r="C582" t="s">
@@ -23533,11 +23588,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>1327</v>
       </c>
-      <c r="B583" t="s">
+      <c r="B583" s="23" t="s">
         <v>1328</v>
       </c>
       <c r="C583" t="s">
@@ -23562,11 +23617,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>1527</v>
       </c>
-      <c r="B584" t="s">
+      <c r="B584" s="23" t="s">
         <v>1528</v>
       </c>
       <c r="C584" t="s">
@@ -23591,11 +23646,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>1531</v>
       </c>
-      <c r="B585" t="s">
+      <c r="B585" s="23" t="s">
         <v>1532</v>
       </c>
       <c r="C585" t="s">
@@ -23620,11 +23675,11 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" s="6" t="s">
         <v>1830</v>
       </c>
-      <c r="B586" s="3" t="s">
+      <c r="B586" s="22" t="s">
         <v>1831</v>
       </c>
       <c r="C586" s="3" t="s">
@@ -23649,11 +23704,11 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" s="17" t="s">
         <v>1930</v>
       </c>
-      <c r="B587" s="5" t="s">
+      <c r="B587" s="24" t="s">
         <v>1831</v>
       </c>
       <c r="C587" t="s">
@@ -23678,11 +23733,11 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" s="17" t="s">
         <v>1931</v>
       </c>
-      <c r="B588" s="5" t="s">
+      <c r="B588" s="24" t="s">
         <v>1831</v>
       </c>
       <c r="C588" t="s">
@@ -23707,11 +23762,11 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" s="17" t="s">
         <v>1840</v>
       </c>
-      <c r="B589" s="5" t="s">
+      <c r="B589" s="24" t="s">
         <v>1831</v>
       </c>
       <c r="C589" t="s">
@@ -23736,11 +23791,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" s="17" t="s">
         <v>1932</v>
       </c>
-      <c r="B590" s="5" t="s">
+      <c r="B590" s="24" t="s">
         <v>1831</v>
       </c>
       <c r="C590" t="s">
@@ -23765,11 +23820,11 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" s="17" t="s">
         <v>1804</v>
       </c>
-      <c r="B591" s="5" t="s">
+      <c r="B591" s="24" t="s">
         <v>1831</v>
       </c>
       <c r="C591" t="s">
@@ -23794,11 +23849,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" s="17" t="s">
         <v>1819</v>
       </c>
-      <c r="B592" s="5" t="s">
+      <c r="B592" s="24" t="s">
         <v>1831</v>
       </c>
       <c r="C592" t="s">
@@ -23823,11 +23878,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" s="17" t="s">
         <v>1939</v>
       </c>
-      <c r="B593" t="s">
+      <c r="B593" s="23" t="s">
         <v>1846</v>
       </c>
       <c r="C593" t="s">
@@ -23852,11 +23907,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" s="17" t="s">
         <v>1798</v>
       </c>
-      <c r="B594" t="s">
+      <c r="B594" s="23" t="s">
         <v>1798</v>
       </c>
       <c r="C594" t="s">
@@ -23881,11 +23936,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" s="17" t="s">
         <v>1940</v>
       </c>
-      <c r="B595" t="s">
+      <c r="B595" s="23" t="s">
         <v>1809</v>
       </c>
       <c r="C595" t="s">
@@ -23910,11 +23965,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" s="20" t="s">
         <v>1941</v>
       </c>
-      <c r="B596" s="5" t="s">
+      <c r="B596" s="24" t="s">
         <v>1795</v>
       </c>
       <c r="C596" s="5" t="s">
@@ -23939,11 +23994,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" s="17" t="s">
         <v>1933</v>
       </c>
-      <c r="B597" t="s">
+      <c r="B597" s="23" t="s">
         <v>1808</v>
       </c>
       <c r="C597" t="s">
@@ -23968,11 +24023,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" s="17" t="s">
         <v>1934</v>
       </c>
-      <c r="B598" t="s">
+      <c r="B598" s="23" t="s">
         <v>1849</v>
       </c>
       <c r="C598" t="s">
@@ -23997,11 +24052,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" s="17" t="s">
         <v>1935</v>
       </c>
-      <c r="B599" t="s">
+      <c r="B599" s="23" t="s">
         <v>1799</v>
       </c>
       <c r="C599" t="s">
@@ -24026,11 +24081,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" s="17" t="s">
         <v>1936</v>
       </c>
-      <c r="B600" t="s">
+      <c r="B600" s="23" t="s">
         <v>1806</v>
       </c>
       <c r="C600" t="s">
@@ -24055,11 +24110,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" s="17" t="s">
         <v>1937</v>
       </c>
-      <c r="B601" t="s">
+      <c r="B601" s="23" t="s">
         <v>1807</v>
       </c>
       <c r="C601" t="s">
@@ -24084,11 +24139,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" s="17" t="s">
         <v>1938</v>
       </c>
-      <c r="B602" t="s">
+      <c r="B602" s="23" t="s">
         <v>1802</v>
       </c>
       <c r="C602" t="s">
@@ -24113,11 +24168,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" s="17" t="s">
         <v>1801</v>
       </c>
-      <c r="B603" t="s">
+      <c r="B603" s="23" t="s">
         <v>1803</v>
       </c>
       <c r="C603" t="s">
@@ -24142,11 +24197,11 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" s="17" t="s">
         <v>1942</v>
       </c>
-      <c r="B604" t="s">
+      <c r="B604" s="23" t="s">
         <v>1815</v>
       </c>
       <c r="C604" t="s">
@@ -24171,11 +24226,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" s="17" t="s">
         <v>1943</v>
       </c>
-      <c r="B605" t="s">
+      <c r="B605" s="23" t="s">
         <v>1817</v>
       </c>
       <c r="C605" t="s">
@@ -24200,11 +24255,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" s="17" t="s">
         <v>1944</v>
       </c>
-      <c r="B606" t="s">
+      <c r="B606" s="23" t="s">
         <v>1834</v>
       </c>
       <c r="C606" t="s">
@@ -24229,11 +24284,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" s="17" t="s">
         <v>1945</v>
       </c>
-      <c r="B607" t="s">
+      <c r="B607" s="23" t="s">
         <v>1800</v>
       </c>
       <c r="C607" t="s">
@@ -24258,11 +24313,11 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" s="17" t="s">
         <v>798</v>
       </c>
-      <c r="B608" t="s">
+      <c r="B608" s="23" t="s">
         <v>1816</v>
       </c>
       <c r="C608" t="s">
@@ -24287,11 +24342,11 @@
         <v>798</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" s="17" t="s">
         <v>1946</v>
       </c>
-      <c r="B609" t="s">
+      <c r="B609" s="23" t="s">
         <v>1816</v>
       </c>
       <c r="C609" t="s">
@@ -24316,11 +24371,11 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" s="17" t="s">
         <v>1947</v>
       </c>
-      <c r="B610" t="s">
+      <c r="B610" s="23" t="s">
         <v>1816</v>
       </c>
       <c r="C610" t="s">
@@ -24345,11 +24400,11 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" s="17" t="s">
         <v>1948</v>
       </c>
-      <c r="B611" t="s">
+      <c r="B611" s="23" t="s">
         <v>1816</v>
       </c>
       <c r="C611" t="s">
@@ -24374,11 +24429,11 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" s="17" t="s">
         <v>1949</v>
       </c>
-      <c r="B612" t="s">
+      <c r="B612" s="23" t="s">
         <v>1816</v>
       </c>
       <c r="C612" t="s">
@@ -24403,11 +24458,11 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" s="17" t="s">
         <v>1833</v>
       </c>
-      <c r="B613" t="s">
+      <c r="B613" s="23" t="s">
         <v>1816</v>
       </c>
       <c r="C613" t="s">
@@ -24432,11 +24487,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" s="17" t="s">
         <v>1848</v>
       </c>
-      <c r="B614" t="s">
+      <c r="B614" s="23" t="s">
         <v>1816</v>
       </c>
       <c r="C614" t="s">
@@ -24461,11 +24516,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" s="17" t="s">
         <v>1839</v>
       </c>
-      <c r="B615" t="s">
+      <c r="B615" s="23" t="s">
         <v>1816</v>
       </c>
       <c r="C615" t="s">
@@ -24490,11 +24545,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" s="17" t="s">
         <v>1953</v>
       </c>
-      <c r="B616" t="s">
+      <c r="B616" s="23" t="s">
         <v>1838</v>
       </c>
       <c r="C616" t="s">
@@ -24519,11 +24574,11 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" s="17" t="s">
         <v>1954</v>
       </c>
-      <c r="B617" t="s">
+      <c r="B617" s="23" t="s">
         <v>1805</v>
       </c>
       <c r="C617" t="s">
@@ -24548,11 +24603,11 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" s="17" t="s">
         <v>1955</v>
       </c>
-      <c r="B618" t="s">
+      <c r="B618" s="23" t="s">
         <v>1847</v>
       </c>
       <c r="C618" t="s">
@@ -24577,11 +24632,11 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" s="17" t="s">
         <v>1956</v>
       </c>
-      <c r="B619" t="s">
+      <c r="B619" s="23" t="s">
         <v>1844</v>
       </c>
       <c r="C619" t="s">
@@ -24606,11 +24661,11 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" s="17" t="s">
         <v>1957</v>
       </c>
-      <c r="B620" t="s">
+      <c r="B620" s="23" t="s">
         <v>1829</v>
       </c>
       <c r="C620" t="s">
@@ -24635,11 +24690,11 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" s="17" t="s">
         <v>1958</v>
       </c>
-      <c r="B621" t="s">
+      <c r="B621" s="23" t="s">
         <v>1820</v>
       </c>
       <c r="C621" t="s">
@@ -24664,11 +24719,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" s="17" t="s">
         <v>1832</v>
       </c>
-      <c r="B622" t="s">
+      <c r="B622" s="23" t="s">
         <v>1818</v>
       </c>
       <c r="C622" t="s">
@@ -24693,11 +24748,11 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" s="17" t="s">
         <v>1950</v>
       </c>
-      <c r="B623" t="s">
+      <c r="B623" s="23" t="s">
         <v>1818</v>
       </c>
       <c r="C623" t="s">
@@ -24722,11 +24777,11 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" s="17" t="s">
         <v>1951</v>
       </c>
-      <c r="B624" t="s">
+      <c r="B624" s="23" t="s">
         <v>1818</v>
       </c>
       <c r="C624" t="s">
@@ -24751,11 +24806,11 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" s="17" t="s">
         <v>1952</v>
       </c>
-      <c r="B625" t="s">
+      <c r="B625" s="23" t="s">
         <v>1818</v>
       </c>
       <c r="C625" t="s">
@@ -24780,11 +24835,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" s="17" t="s">
         <v>739</v>
       </c>
-      <c r="B626" t="s">
+      <c r="B626" s="23" t="s">
         <v>1983</v>
       </c>
       <c r="C626" t="s">
@@ -24809,11 +24864,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" s="17" t="s">
         <v>1821</v>
       </c>
-      <c r="B627" t="s">
+      <c r="B627" s="23" t="s">
         <v>1983</v>
       </c>
       <c r="C627" t="s">
@@ -24838,11 +24893,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" s="17" t="s">
         <v>1841</v>
       </c>
-      <c r="B628" t="s">
+      <c r="B628" s="23" t="s">
         <v>1983</v>
       </c>
       <c r="C628" t="s">
@@ -24867,11 +24922,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" s="17" t="s">
         <v>1824</v>
       </c>
-      <c r="B629" t="s">
+      <c r="B629" s="23" t="s">
         <v>1983</v>
       </c>
       <c r="C629" t="s">
@@ -24896,11 +24951,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" s="17" t="s">
         <v>1827</v>
       </c>
-      <c r="B630" t="s">
+      <c r="B630" s="23" t="s">
         <v>1983</v>
       </c>
       <c r="C630" t="s">
@@ -24925,11 +24980,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" s="17" t="s">
         <v>1959</v>
       </c>
-      <c r="B631" t="s">
+      <c r="B631" s="23" t="s">
         <v>1983</v>
       </c>
       <c r="C631" t="s">
@@ -24954,11 +25009,11 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" s="17" t="s">
         <v>1960</v>
       </c>
-      <c r="B632" t="s">
+      <c r="B632" s="23" t="s">
         <v>1983</v>
       </c>
       <c r="C632" t="s">
@@ -24983,11 +25038,11 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" s="17" t="s">
         <v>1287</v>
       </c>
-      <c r="B633" t="s">
+      <c r="B633" s="23" t="s">
         <v>1985</v>
       </c>
       <c r="C633" t="s">
@@ -25012,11 +25067,11 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" s="17" t="s">
         <v>1837</v>
       </c>
-      <c r="B634" t="s">
+      <c r="B634" s="23" t="s">
         <v>1985</v>
       </c>
       <c r="C634" t="s">
@@ -25041,11 +25096,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" s="17" t="s">
         <v>1812</v>
       </c>
-      <c r="B635" t="s">
+      <c r="B635" s="23" t="s">
         <v>1985</v>
       </c>
       <c r="C635" t="s">
@@ -25070,11 +25125,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" s="17" t="s">
         <v>1845</v>
       </c>
-      <c r="B636" t="s">
+      <c r="B636" s="23" t="s">
         <v>1985</v>
       </c>
       <c r="C636" t="s">
@@ -25099,11 +25154,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" s="17" t="s">
         <v>1797</v>
       </c>
-      <c r="B637" t="s">
+      <c r="B637" s="23" t="s">
         <v>1985</v>
       </c>
       <c r="C637" t="s">
@@ -25128,11 +25183,11 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" s="17" t="s">
         <v>1961</v>
       </c>
-      <c r="B638" t="s">
+      <c r="B638" s="23" t="s">
         <v>1985</v>
       </c>
       <c r="C638" t="s">
@@ -25157,11 +25212,11 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" s="17" t="s">
         <v>1971</v>
       </c>
-      <c r="B639" t="s">
+      <c r="B639" s="23" t="s">
         <v>1963</v>
       </c>
       <c r="E639" t="s">
@@ -25180,11 +25235,11 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" s="17" t="s">
         <v>1970</v>
       </c>
-      <c r="B640" t="s">
+      <c r="B640" s="23" t="s">
         <v>1965</v>
       </c>
       <c r="E640" t="s">
@@ -25203,11 +25258,11 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" s="17" t="s">
         <v>1966</v>
       </c>
-      <c r="B641" t="s">
+      <c r="B641" s="23" t="s">
         <v>1967</v>
       </c>
       <c r="E641" t="s">
@@ -25226,11 +25281,11 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" s="17" t="s">
         <v>1969</v>
       </c>
-      <c r="B642" t="s">
+      <c r="B642" s="23" t="s">
         <v>1972</v>
       </c>
       <c r="E642" t="s">
@@ -25249,11 +25304,11 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" s="17" t="s">
         <v>1974</v>
       </c>
-      <c r="B643" t="s">
+      <c r="B643" s="23" t="s">
         <v>1975</v>
       </c>
       <c r="E643" t="s">
@@ -25272,11 +25327,11 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" s="17" t="s">
         <v>1978</v>
       </c>
-      <c r="B644" t="s">
+      <c r="B644" s="23" t="s">
         <v>1979</v>
       </c>
       <c r="E644" t="s">
@@ -25295,11 +25350,11 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" s="17" t="s">
         <v>1981</v>
       </c>
-      <c r="B645" t="s">
+      <c r="B645" s="23" t="s">
         <v>1982</v>
       </c>
       <c r="E645" t="s">
@@ -25316,6 +25371,422 @@
       </c>
       <c r="I645" s="18" t="s">
         <v>1984</v>
+      </c>
+    </row>
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A646" s="17" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B646" s="23" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C646" t="s">
+        <v>839</v>
+      </c>
+      <c r="D646" t="s">
+        <v>840</v>
+      </c>
+      <c r="E646" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F646" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G646" s="25">
+        <v>1043</v>
+      </c>
+      <c r="H646">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>5</v>
+      </c>
+      <c r="B647" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C647" t="s">
+        <v>7</v>
+      </c>
+      <c r="D647" t="s">
+        <v>8</v>
+      </c>
+      <c r="E647" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F647" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G647" s="25">
+        <v>238</v>
+      </c>
+      <c r="H647">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A648" t="s">
+        <v>14</v>
+      </c>
+      <c r="B648" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C648" t="s">
+        <v>16</v>
+      </c>
+      <c r="D648" t="s">
+        <v>17</v>
+      </c>
+      <c r="E648" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F648" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G648" s="25">
+        <v>82</v>
+      </c>
+      <c r="H648">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A649" t="s">
+        <v>83</v>
+      </c>
+      <c r="B649" s="23" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C649" t="s">
+        <v>84</v>
+      </c>
+      <c r="D649" t="s">
+        <v>85</v>
+      </c>
+      <c r="E649" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F649" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G649" s="25">
+        <v>501</v>
+      </c>
+      <c r="H649">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A650" t="s">
+        <v>134</v>
+      </c>
+      <c r="B650" s="23" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C650" t="s">
+        <v>135</v>
+      </c>
+      <c r="D650" t="s">
+        <v>136</v>
+      </c>
+      <c r="E650" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F650" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G650" s="25">
+        <v>203</v>
+      </c>
+      <c r="H650">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A651" t="s">
+        <v>607</v>
+      </c>
+      <c r="B651" s="23" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C651" t="s">
+        <v>609</v>
+      </c>
+      <c r="D651" t="s">
+        <v>610</v>
+      </c>
+      <c r="E651" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F651" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G651" s="25">
+        <v>395</v>
+      </c>
+      <c r="H651">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A652" t="s">
+        <v>647</v>
+      </c>
+      <c r="B652" s="23" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C652" t="s">
+        <v>649</v>
+      </c>
+      <c r="D652" t="s">
+        <v>650</v>
+      </c>
+      <c r="E652" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F652" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G652" s="25">
+        <v>491</v>
+      </c>
+      <c r="H652">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A653" t="s">
+        <v>631</v>
+      </c>
+      <c r="B653" s="23" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C653" t="s">
+        <v>633</v>
+      </c>
+      <c r="D653" t="s">
+        <v>634</v>
+      </c>
+      <c r="E653" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F653" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G653" s="25">
+        <v>477</v>
+      </c>
+      <c r="H653">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A654" t="s">
+        <v>639</v>
+      </c>
+      <c r="B654" s="23" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C654" t="s">
+        <v>641</v>
+      </c>
+      <c r="D654" t="s">
+        <v>642</v>
+      </c>
+      <c r="E654" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F654" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G654" s="25">
+        <v>688</v>
+      </c>
+      <c r="H654">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A655" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B655" s="23" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C655" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D655" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E655" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F655" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G655" s="25">
+        <v>329</v>
+      </c>
+      <c r="H655">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A656" t="s">
+        <v>790</v>
+      </c>
+      <c r="B656" s="23" t="s">
+        <v>1999</v>
+      </c>
+      <c r="C656" t="s">
+        <v>792</v>
+      </c>
+      <c r="D656" t="s">
+        <v>793</v>
+      </c>
+      <c r="E656" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F656" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G656" s="25">
+        <v>364</v>
+      </c>
+      <c r="H656">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A657" t="s">
+        <v>919</v>
+      </c>
+      <c r="B657" s="23" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C657" t="s">
+        <v>921</v>
+      </c>
+      <c r="D657" t="s">
+        <v>922</v>
+      </c>
+      <c r="E657" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F657" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G657" s="25">
+        <v>871</v>
+      </c>
+      <c r="H657">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A658" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B658" s="23" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C658" t="s">
+        <v>835</v>
+      </c>
+      <c r="D658" t="s">
+        <v>836</v>
+      </c>
+      <c r="E658" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F658" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G658" s="25">
+        <v>328</v>
+      </c>
+      <c r="H658">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="659" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>967</v>
+      </c>
+      <c r="B659" s="23" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C659" t="s">
+        <v>969</v>
+      </c>
+      <c r="D659" t="s">
+        <v>970</v>
+      </c>
+      <c r="E659" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F659" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G659" s="25">
+        <v>207</v>
+      </c>
+      <c r="H659">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="660" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B660" s="23" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C660" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D660" t="s">
+        <v>1792</v>
+      </c>
+      <c r="E660" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F660" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G660" s="25">
+        <v>768</v>
+      </c>
+      <c r="H660">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="661" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A661" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B661" s="23" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C661" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D661" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E661" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F661" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G661" s="25">
+        <v>147</v>
+      </c>
+      <c r="H661">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
